--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -478,7 +478,7 @@
         <v>76029</v>
       </c>
       <c r="C2" t="n">
-        <v>41004</v>
+        <v>44236</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -500,7 +500,7 @@
         <v>1522</v>
       </c>
       <c r="C3" t="n">
-        <v>1277</v>
+        <v>1249</v>
       </c>
       <c r="D3">
         <f>C3-B3</f>
@@ -676,7 +676,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>3919</v>
+        <v>3776</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -698,7 +698,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>4258</v>
+        <v>4323</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -808,7 +808,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>15786</v>
+        <v>17011</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -830,7 +830,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>4988</v>
+        <v>4806</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -852,7 +852,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>9866</v>
+        <v>10632</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -918,7 +918,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>4604</v>
+        <v>4961</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -959,7 +959,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1227 кг, стало 760 кг; площадь окраски 57.5 → 41.0 м²; швы 37.6 → 24.2 м; деталей 84 → 68.</t>
+          <t>Масса металла: было 1227 кг, стало 730 кг; площадь окраски 57.5 → 39.5 м²; швы 37.6 → 24.6 м; деталей 84 → 74.</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1053,188 +1053,161 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Стропила</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.53</v>
+        <v>20.72</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>143.2</v>
+        <v>146.5</v>
       </c>
       <c r="F3" t="n">
-        <v>540</v>
+        <v>428</v>
       </c>
       <c r="G3" t="n">
-        <v>8387</v>
+        <v>8868</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×50×4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Колонны</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.72</v>
+        <v>15.53</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>156</v>
+        <v>133.5</v>
       </c>
       <c r="F4" t="n">
-        <v>348</v>
+        <v>522</v>
       </c>
       <c r="G4" t="n">
-        <v>7211</v>
+        <v>8108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□60×60×2,5</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Затяжки</t>
+          <t>Затяжки, Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.36</v>
+        <v>26.25</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>71.8</v>
+        <v>93.5</v>
       </c>
       <c r="F5" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="G5" t="n">
-        <v>3010</v>
+        <v>5933</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□80×40×2,2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Подвеска (стойка у конька), Подкосы фермы</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.890000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>38.5</v>
+        <v>9.1</v>
       </c>
       <c r="F6" t="n">
-        <v>150</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>1484</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□25×25×2</t>
+          <t>□70×70×2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька)</t>
+          <t>Стойка-вставка средней рамы</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.05</v>
+        <v>0.21</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="F7" t="n">
-        <v>91.09999999999999</v>
+        <v>264</v>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□80×40×2,5</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Стойка-вставка средней рамы</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>182</v>
-      </c>
-      <c r="G8" t="n">
-        <v>37</v>
+          <t>ИТОГО трубы</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUM(C2:C7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUM(G2:G7)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ИТОГО трубы</t>
-        </is>
-      </c>
-      <c r="C9">
-        <f>SUM(C2:C8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>SUM(G2:G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Пластины (фасонки, крышки колонн): 23.2 кг × 55 грн/кг</t>
+          <t>Пластины (фасонки, крышки колонн): 22.7 кг × 55 грн/кг</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1300,7 +1273,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×50×4</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1310,7 +1283,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>143.1</v>
+        <v>133.4</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -1322,7 +1295,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1332,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>83.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -1344,7 +1317,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1354,7 +1327,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>72.2</v>
+        <v>67.8</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -1366,7 +1339,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>□60×60×2,5</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1376,7 +1349,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>71.7</v>
+        <v>58.2</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -1388,7 +1361,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>□25×25×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1398,101 +1371,123 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Подкосы фермы</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.98</v>
+        <v>1.104</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>305.8</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>стык на раме: 2 заготовки</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Обрешётка</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>□80×40×2,2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.47</v>
+        <v>6.98</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>305.8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>стык на раме: 2 заготовки</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.6</v>
+        <v>2.47</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>18.3</v>
+        <v>35.2</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□80×40×2,5</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1</v>
+        <v>4.6</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>18.3</v>
       </c>
       <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Стойка-вставка средней рамы</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>□70×70×2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1505,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1545,7 +1540,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×50×4</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1568,7 +1563,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×50×4</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1591,7 +1586,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×50×4</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1614,7 +1609,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×50×4</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1637,7 +1632,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1660,7 +1655,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1683,7 +1678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1706,7 +1701,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1729,7 +1724,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1752,7 +1747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1775,7 +1770,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>□60×60×2,5</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1798,7 +1793,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>□60×60×2,5</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1821,7 +1816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>□60×60×2,5</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1844,93 +1839,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>□25×25×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.679 + 0.679 + 0.679</t>
+          <t>2.470 + 2.470</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька)</t>
+          <t>Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.954</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>2.470 + 2.470</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-0.003</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>1.104 + 1.104 + 1.104 + 1.104 + 1.104</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Подкосы фермы</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-0.003</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>1.104 + 0.679 + 0.679 + 0.679</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Подвеска (стойка у конька); Подкосы фермы</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-0.003</v>
+        <v>2.847</v>
       </c>
     </row>
     <row r="19">
@@ -1940,7 +1935,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1963,7 +1958,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1986,7 +1981,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2009,7 +2004,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2032,7 +2027,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2055,7 +2050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2078,7 +2073,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2101,7 +2096,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2124,7 +2119,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2147,7 +2142,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2170,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2193,7 +2188,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2216,7 +2211,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2239,7 +2234,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2262,7 +2257,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2285,7 +2280,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2308,7 +2303,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2331,7 +2326,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2354,7 +2349,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2377,20 +2372,20 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4.600 + 0.980</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы; Обрешётка</t>
+          <t>Обрешётка (часть)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.414</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="39">
@@ -2400,20 +2395,20 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.600 + 0.980</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы; Обрешётка</t>
+          <t>Обрешётка (часть)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.414</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="40">
@@ -2423,20 +2418,20 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Обрешётка (часть)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.102</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="41">
@@ -2446,20 +2441,20 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
+          <t>4.600 + 0.980</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Нижний пояс боковой фермы; Обрешётка</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.102</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="42">
@@ -2469,20 +2464,20 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
+          <t>4.600 + 0.980</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Нижний пояс боковой фермы; Обрешётка</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.102</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="43">
@@ -2492,11 +2487,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.980 + 0.980</t>
+          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2505,75 +2500,98 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4.034</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>□80×40×2,2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2.470 + 2.470</t>
+          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Обрешётка</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.054</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>□80×40×2,2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.470 + 2.470</t>
+          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Обрешётка</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.054</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>□80×40×2,5</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>28</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0.980 + 0.980</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Обрешётка</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4.034</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>□70×70×2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
         <v>1</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>0.100 + 0.100</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Стойка-вставка средней рамы</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>5.794</v>
       </c>
     </row>
@@ -2588,7 +2606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2645,20 +2663,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×50×4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.06</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.544</v>
+        <v>2.488</v>
       </c>
       <c r="F2" t="n">
-        <v>0.878</v>
+        <v>0.928</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2674,20 +2692,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□100×100×2,5</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.08</v>
+        <v>28.11</v>
       </c>
       <c r="D3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="E3" t="n">
-        <v>4.087</v>
+        <v>4.066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.886</v>
+        <v>0.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2703,20 +2721,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>□60×60×2,5</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02</v>
+        <v>0.51</v>
       </c>
       <c r="D4" t="n">
-        <v>24.1</v>
+        <v>26.39</v>
       </c>
       <c r="E4" t="n">
-        <v>0.394</v>
+        <v>0.368</v>
       </c>
       <c r="F4" t="n">
-        <v>0.78</v>
+        <v>0.772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2732,138 +2750,167 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>□25×25×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>1.68</v>
       </c>
       <c r="E5" t="n">
-        <v>0.099</v>
+        <v>0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>0.413</v>
+        <v>0.31</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>устойчивость [D+S(лів.)]</t>
+          <t>узел kp→tie: продавливание грани пояса N=1.7 кН, NRd=5.4 кН</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Подкосы фермы</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.79</v>
+        <v>5.63</v>
       </c>
       <c r="D6" t="n">
-        <v>1.99</v>
+        <v>2.76</v>
       </c>
       <c r="E6" t="n">
-        <v>0.438</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.887</v>
+        <v>0.896</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>прочность [D+S+0.9W+x]</t>
+          <t>гибкость [D+S(лів.)]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Обрешётка</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>□80×40×2,2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.31</v>
+        <v>0.86</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.438</v>
       </c>
       <c r="F7" t="n">
-        <v>0.845</v>
+        <v>0.887</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>гибкость [D+S+0.9W+y]</t>
+          <t>прочность [D+S+0.9W-x]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="n">
-        <v>16.81</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.046</v>
+        <v>0.183</v>
       </c>
       <c r="F8" t="n">
-        <v>0.864</v>
+        <v>0.643</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>гибкость раст. [D+S]</t>
+          <t>стенка c/t [D+S]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>гибкость раст. [D+S]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Стойка-вставка средней рамы</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>□80×40×2,5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>□70×70×2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="E10" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>устойчивость [D+S+0.9W+y]</t>
         </is>
@@ -2920,315 +2967,315 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, попер. подкосы, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>180351</v>
+        <v>185164</v>
       </c>
       <c r="C2" t="n">
-        <v>39730</v>
+        <v>44236</v>
       </c>
       <c r="D2" t="n">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □25×25×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Колонны: □100×50×3,8</t>
+          <t>Подкосы фермы: □20×20×2; Нижний пояс боковой фермы: □35×35×2; Колонны: □100×50×4; Раскосы боковой фермы: □60×60×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □35×35×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, попер. подкосы, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>181783</v>
+        <v>185802</v>
       </c>
       <c r="C3" t="n">
-        <v>38843</v>
+        <v>46085</v>
       </c>
       <c r="D3" t="n">
-        <v>739</v>
+        <v>757</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □80×80×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Колонны: □100×50×3,8</t>
+          <t>Нижний пояс боковой фермы: □35×35×2; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □100×60×4; Раскосы боковой фермы: □50×50×2; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □40×30×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, без попер. подкосов, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>182220</v>
+        <v>185863</v>
       </c>
       <c r="C4" t="n">
-        <v>43482</v>
+        <v>43344</v>
       </c>
       <c r="D4" t="n">
-        <v>765</v>
+        <v>726</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □25×25×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Колонны: □100×50×3,8</t>
+          <t>Подкосы фермы: □30×20×2; Нижний пояс боковой фермы: □35×35×2; Колонны: □80×80×4; Раскосы боковой фермы: □50×50×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □35×35×2; Подкосы колонна→затяжка: □20×20×2; Затяжки: □45×45×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>182385</v>
+        <v>186096</v>
       </c>
       <c r="C5" t="n">
-        <v>40596</v>
+        <v>47254</v>
       </c>
       <c r="D5" t="n">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,5; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Затяжки: □60×60×2,5; Подвеска (стойка у конька): □25×25×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Подкосы фермы: □30×20×2; Колонны: □100×50×3,8</t>
+          <t>Нижний пояс боковой фермы: □35×35×2; Колонны: □120×80×4; Раскосы боковой фермы: □50×50×2; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □40×30×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, попер. подкосы, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>183194</v>
+        <v>186815</v>
       </c>
       <c r="C6" t="n">
-        <v>41093</v>
+        <v>44774</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>746</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Верхний пояс боковой фермы / обвязка: □40×40×2; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □25×25×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Колонны: □100×50×3,8</t>
+          <t>Подкосы фермы: □20×20×2; Нижний пояс боковой фермы: □35×35×2; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □80×80×4; Раскосы боковой фермы: □50×50×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □35×35×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска + подкосы фермы, попер. подкосы, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>184626</v>
+        <v>186866</v>
       </c>
       <c r="C7" t="n">
-        <v>40205</v>
+        <v>45451</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □80×80×3; Верхний пояс боковой фермы / обвязка: □40×40×2; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Колонны: □100×50×3,8</t>
+          <t>Нижний пояс боковой фермы: □35×35×2; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □80×80×4; Раскосы боковой фермы: □50×50×2; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □40×30×2; Подкосы колонна→затяжка: □20×20×2; Затяжки: □60×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, без попер. подкосов, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>185064</v>
+        <v>187661</v>
       </c>
       <c r="C8" t="n">
-        <v>44845</v>
+        <v>46987</v>
       </c>
       <c r="D8" t="n">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×3; Верхний пояс боковой фермы / обвязка: □40×40×2; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □25×25×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Колонны: □100×50×3,8</t>
+          <t>Нижний пояс боковой фермы: □35×35×2; Колонны: □120×80×4; Раскосы боковой фермы: □50×50×2; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □40×30×2; Подкосы колонна→затяжка: □20×20×2; Затяжки: □60×40×2; Подвеска (стойка у конька): □40×25×2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска + подкосы фермы, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185224</v>
+        <v>188850</v>
       </c>
       <c r="C9" t="n">
-        <v>41951</v>
+        <v>44710</v>
       </c>
       <c r="D9" t="n">
-        <v>774</v>
+        <v>742</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Верхний пояс боковой фермы / обвязка: □40×40×2; Затяжки: □60×60×2,5; Подвеска (стойка у конька): □25×25×2; Нижний пояс боковой фермы: □35×35×2; Раскосы боковой фермы: □80×40×2,2; Подкосы фермы: □30×20×2; Колонны: □100×50×3,8</t>
+          <t>Подкосы фермы: □20×20×2; Нижний пояс боковой фермы: □35×35×2; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □100×50×3,8; Раскосы боковой фермы: □60×60×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □80×40×4; Обрешётка: □35×35×2; Подкосы колонна→затяжка: □40×20×2; Затяжки: □60×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, попер. подкосы, без связей</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>187385</v>
+        <v>193948</v>
       </c>
       <c r="C10" t="n">
-        <v>50139</v>
+        <v>45056</v>
       </c>
       <c r="D10" t="n">
-        <v>1062</v>
+        <v>750</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □120×80×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Продольная обвязка: □35×35×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □20×20×2; Нижний пояс боковой фермы: □40×40×2; Колонны: □80×80×4; Связи по скатам: □20×20×2; Раскосы боковой фермы: □50×50×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □35×35×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, попер. подкосы, связи по скатам</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>191818</v>
+        <v>195345</v>
       </c>
       <c r="C11" t="n">
-        <v>43167</v>
+        <v>44771</v>
       </c>
       <c r="D11" t="n">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Затяжки: □40×40×2; Подвеска (стойка у конька): □25×25×2; Нижний пояс боковой фермы: □35×35×2; Связи по скатам: □20×20×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Колонны: □120×60×3,8</t>
+          <t>Подкосы фермы: □20×20×2; Нижний пояс боковой фермы: □35×35×2; Колонны: □80×80×4; Связи по скатам: □20×20×2; Раскосы боковой фермы: □50×50×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □80×60×2; Обрешётка: □35×35×2; Подкосы колонна→затяжка: □20×20×2; Затяжки: □50×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>191935</v>
+        <v>195785</v>
       </c>
       <c r="C12" t="n">
-        <v>41991</v>
+        <v>46929</v>
       </c>
       <c r="D12" t="n">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Затяжки: □60×60×2,5; Подвеска (стойка у конька): □20×20×2; Нижний пояс боковой фермы: □35×35×2; Связи по скатам: □20×20×2; Раскосы боковой фермы: □80×40×2,2; Подкосы фермы: □30×20×2; Колонны: □100×50×3,8</t>
+          <t>Нижний пояс боковой фермы: □40×40×2,1; Колонны: □80×80×4; Связи по скатам: □50×20×2; Раскосы боковой фермы: □50×50×2; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □80×40×4; Обрешётка: □35×35×2; Подкосы колонна→затяжка: □20×20×2; Затяжки: □60×40×2; Подвеска (стойка у конька): □30×20×2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
+          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>192905</v>
+        <v>196503</v>
       </c>
       <c r="C13" t="n">
-        <v>41670</v>
+        <v>46225</v>
       </c>
       <c r="D13" t="n">
-        <v>745</v>
+        <v>769</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2; Нижний пояс боковой фермы: □35×35×2; Связи по скатам: □20×20×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Колонны: □100×50×3,8</t>
+          <t>Подкосы фермы: □20×20×2; Нижний пояс боковой фермы: □35×35×2; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □80×80×4; Связи по скатам: □20×20×2; Раскосы боковой фермы: □50×50×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □35×35×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, попер. подкосы, связи по скатам</t>
+          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>193050</v>
+        <v>196908</v>
       </c>
       <c r="C14" t="n">
-        <v>43177</v>
+        <v>48576</v>
       </c>
       <c r="D14" t="n">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Верхний пояс боковой фермы / обвязка: □40×40×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2; Нижний пояс боковой фермы: □35×35×2; Связи по скатам: □20×20×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Колонны: □80×80×4</t>
+          <t>Нижний пояс боковой фермы: □50×30×2 пл.; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □100×50×3,8; Связи по скатам: □50×20×2; Раскосы боковой фермы: □45×45×3; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □90×30×2; Обрешётка: □40×30×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □30×20×2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
+          <t>2 рамы (только по колоннам), подвеска, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>194779</v>
+        <v>196961</v>
       </c>
       <c r="C15" t="n">
-        <v>43354</v>
+        <v>63623</v>
       </c>
       <c r="D15" t="n">
-        <v>796</v>
+        <v>1060</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □100×100×2,5; Верхний пояс боковой фермы / обвязка: □40×40×2; Затяжки: □60×60×2,5; Подвеска (стойка у конька): □20×20×2; Нижний пояс боковой фермы: □35×35×2; Связи по скатам: □20×20×2; Раскосы боковой фермы: □80×40×2,2; Подкосы фермы: □30×20×2; Колонны: □100×50×3,8</t>
+          <t>Колонны: □140×140×4; Стропила: □160×80×4; Обрешётка: □60×60×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, без попер. подкосов, связи по скатам</t>
+          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>194788</v>
+        <v>198474</v>
       </c>
       <c r="C16" t="n">
-        <v>46724</v>
+        <v>48172</v>
       </c>
       <c r="D16" t="n">
-        <v>819</v>
+        <v>794</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □40×40×2; Стропила: □100×100×2,5; Затяжки: □40×40×2; Подвеска (стойка у конька): □25×25×2,1; Нижний пояс боковой фермы: □40×40×2; Связи по скатам: □30×20×2; Раскосы боковой фермы: □80×40×2,2; Колонны: □120×60×3,8</t>
+          <t>Нижний пояс боковой фермы: □45×45×2; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □100×50×3,8; Связи по скатам: □50×20×2; Раскосы боковой фермы: □45×45×3; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □90×30×2; Обрешётка: □35×35×2; Подкосы колонна→затяжка: □20×20×2; Затяжки: □60×40×2; Подвеска (стойка у конька): □40×40×2</t>
         </is>
       </c>
     </row>
@@ -3239,437 +3286,437 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>195428</v>
+        <v>198495</v>
       </c>
       <c r="C17" t="n">
-        <v>42373</v>
+        <v>46440</v>
       </c>
       <c r="D17" t="n">
-        <v>803</v>
+        <v>768</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □35×35×2; Стропила: □80×80×3; Верхний пояс боковой фермы / обвязка: □80×40×2,2; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Нижний пояс боковой фермы: □35×35×2; Связи по скатам: □20×20×2; Раскосы боковой фермы: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Колонны: □100×50×4</t>
+          <t>Подкосы фермы: □20×20×2; Нижний пояс боковой фермы: □35×35×2; Верхний пояс боковой фермы / обвязка: □40×40×2; Колонны: □80×80×4; Связи по скатам: □20×20×2; Раскосы боковой фермы: □50×50×2; Стропила: □100×60×3; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □40×30×2; Подкосы колонна→затяжка: □20×20×2; Затяжки: □50×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
+          <t>3 рамы (средняя на боковых фермах), без верхн. пояса, низ. пояс +2.10, подвеска, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>197962</v>
+        <v>198519</v>
       </c>
       <c r="C18" t="n">
-        <v>52198</v>
+        <v>50534</v>
       </c>
       <c r="D18" t="n">
-        <v>1128</v>
+        <v>833</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □120×80×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Связи по скатам: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Колонны: □100×100×3,8</t>
+          <t>Нижний пояс боковой фермы: □40×40×2; Колонны: □120×80×4; Связи по скатам: □50×20×2; Раскосы боковой фермы: □45×45×3; Стропила: □120×60×2,8; Стойка-вставка средней рамы: □70×70×2; Обрешётка: □35×35×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □40×40×2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
+          <t>2 рамы (только по колоннам), подвеска, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>198217</v>
+        <v>198842</v>
       </c>
       <c r="C19" t="n">
-        <v>54334</v>
+        <v>63543</v>
       </c>
       <c r="D19" t="n">
-        <v>1154</v>
+        <v>1060</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □100×100×3,8; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Связи по скатам: □80×40×2,2; Подкосы фермы: □30×20×2; Колонны: □100×100×3,8</t>
+          <t>Колонны: □140×140×4; Стропила: □160×80×4; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □40×20×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>198315</v>
+        <v>199515</v>
       </c>
       <c r="C20" t="n">
-        <v>53099</v>
+        <v>64793</v>
       </c>
       <c r="D20" t="n">
-        <v>1142</v>
+        <v>1078</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □120×80×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Связи по скатам: □80×40×2,2; Подкосы фермы: □30×20×2; Продольная обвязка: □35×35×2; Колонны: □100×100×3,8</t>
+          <t>Колонны: □140×140×4; Стропила: □160×80×4; Продольная обвязка: □35×35×2; Обрешётка: □60×60×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, попер. подкосы, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>199016</v>
+        <v>201397</v>
       </c>
       <c r="C21" t="n">
-        <v>61265</v>
+        <v>64712</v>
       </c>
       <c r="D21" t="n">
-        <v>1014</v>
+        <v>1078</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □120×80×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Колонны: □100×100×3,8</t>
+          <t>Колонны: □140×140×4; Стропила: □160×80×4; Продольная обвязка: □35×35×2; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □40×20×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), подвеска, без попер. подкосов, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>199168</v>
+        <v>202118</v>
       </c>
       <c r="C22" t="n">
-        <v>64834</v>
+        <v>63037</v>
       </c>
       <c r="D22" t="n">
-        <v>1076</v>
+        <v>1025</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Обрешётка: □80×60×2 пл.; Стропила: □160×80×4; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □30×20×2; Продольные подкосы: □30×20×2; Колонны: □100×100×3,8; Стропила: □120×80×3; Продольная обвязка: □30×20×2 пл.; Обрешётка: □70×70×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, без попер. подкосов, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>199272</v>
+        <v>203878</v>
       </c>
       <c r="C23" t="n">
-        <v>63401</v>
+        <v>62953</v>
       </c>
       <c r="D23" t="n">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □100×100×3,8; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Подкосы фермы: □30×20×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □30×20×2; Продольные подкосы: □30×20×2; Колонны: □100×100×3,8; Стропила: □120×80×3; Продольная обвязка: □30×20×2 пл.; Обрешётка: □70×70×2; Подкосы колонна→затяжка: □30×20×2; Затяжки: □60×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
+          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>199760</v>
+        <v>205070</v>
       </c>
       <c r="C24" t="n">
-        <v>52881</v>
+        <v>68215</v>
       </c>
       <c r="D24" t="n">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □120×80×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Связи по скатам: □80×40×2,2; Подкосы фермы: □30×20×2; Продольная обвязка: □20×20×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □20×20×2; Колонны: □140×140×4; Стропила: □120×80×4; Обрешётка: □70×70×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3 рамы (средняя на боковых фермах), верхн. пояс, низ. пояс +2.10, подвеска, без попер. подкосов, связи по скатам</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>199798</v>
+        <v>205097</v>
       </c>
       <c r="C25" t="n">
-        <v>49794</v>
+        <v>67173</v>
       </c>
       <c r="D25" t="n">
-        <v>871</v>
+        <v>1100</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы: □80×40×2,2; Обрешётка: □40×40×2; Стропила: □100×100×2,5; Верхний пояс боковой фермы / обвязка: □40×40×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □30×20×2; Нижний пояс боковой фермы: □40×40×2; Связи по скатам: □30×25×2; Раскосы боковой фермы: □80×40×2,2; Колонны: □120×80×4</t>
+          <t>Продольные подкосы: □30×20×2; Колонны: □100×100×3,8; Стропила: □160×80×4; Продольная обвязка: □60×40×2; Обрешётка: □70×70×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □30×20×2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
+          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200074</v>
+        <v>205748</v>
       </c>
       <c r="C26" t="n">
-        <v>60818</v>
+        <v>66759</v>
       </c>
       <c r="D26" t="n">
-        <v>1024</v>
+        <v>1105</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □120×80×3; Затяжки: □80×80×3; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Подкосы фермы: □30×20×2; Продольная обвязка: □20×20×2; Колонны: □100×100×3</t>
+          <t>Подкосы фермы: □30×20×2; Колонны: □140×140×4; Стропила: □120×80×3; Обрешётка: □70×70×2; Подкосы колонна→затяжка: □40×20×2; Затяжки: □45×45×3; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>200213</v>
+        <v>205957</v>
       </c>
       <c r="C27" t="n">
-        <v>53077</v>
+        <v>67453</v>
       </c>
       <c r="D27" t="n">
-        <v>1138</v>
+        <v>1114</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □100×100×2,8; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Связи по скатам: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Продольная обвязка: □35×35×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □30×20×2; Колонны: □140×140×4; Стропила: □120×80×3; Продольная обвязка: □35×35×2; Обрешётка: □70×70×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, без попер. подкосов, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>200668</v>
+        <v>206733</v>
       </c>
       <c r="C28" t="n">
-        <v>64098</v>
+        <v>67020</v>
       </c>
       <c r="D28" t="n">
-        <v>1042</v>
+        <v>1099</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □120×80×4; Затяжки: □40×25×2 пл.; Подвеска (стойка у конька): □20×20×2; Подкосы фермы: □20×20×2; Продольная обвязка: □35×35×2; Колонны: □100×100×3,8</t>
+          <t>Продольные подкосы: □30×20×2; Колонны: □100×100×3,8; Стропила: □160×80×4; Продольная обвязка: □60×40×2; Обрешётка: □70×70×2; Подкосы колонна→затяжка: □30×20×2; Затяжки: □40×40×2,1; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска, без попер. подкосов, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, попер. подкосы, без связей</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>200968</v>
+        <v>208302</v>
       </c>
       <c r="C29" t="n">
-        <v>65774</v>
+        <v>67928</v>
       </c>
       <c r="D29" t="n">
-        <v>1074</v>
+        <v>1123</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Обрешётка: □80×60×2; Стропила: □160×80×4; Затяжки: □40×30×2 пл.; Подвеска (стойка у конька): □20×20×2; Продольная обвязка: □35×35×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □30×20×2; Колонны: □140×140×4; Стропила: □120×80×3; Продольная обвязка: □35×35×2; Обрешётка: □70×70×2; Подкосы колонна→затяжка: □40×20×2; Затяжки: □45×45×3; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, без попер. подкосов, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>201779</v>
+        <v>210166</v>
       </c>
       <c r="C30" t="n">
-        <v>65156</v>
+        <v>64414</v>
       </c>
       <c r="D30" t="n">
-        <v>1072</v>
+        <v>1059</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Обрешётка: □80×60×2; Стропила: □160×80×4; Затяжки: □30×25×2; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Продольная обвязка: □20×20×2; Колонны: □120×80×4</t>
+          <t>Подкосы фермы: □30×20×2; Колонны: □140×100×4; Связи по скатам: □70×70×2; Стропила: □120×80×3; Продольная обвязка: □35×35×2; Обрешётка: □60×60×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>201836</v>
+        <v>210815</v>
       </c>
       <c r="C31" t="n">
-        <v>53102</v>
+        <v>63203</v>
       </c>
       <c r="D31" t="n">
-        <v>1150</v>
+        <v>1019</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □120×80×3; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Связи по скатам: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Продольная обвязка: □20×20×2; Колонны: □120×80×4</t>
+          <t>Подкосы фермы: □30×20×2; Продольные подкосы: □30×20×2; Колонны: □100×100×3,8; Связи по скатам: □70×70×2; Стропила: □100×100×2,8; Продольная обвязка: □60×40×2; Обрешётка: □60×60×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □25×25×2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), подвеска, попер. подкосы, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>201862</v>
+        <v>210850</v>
       </c>
       <c r="C32" t="n">
-        <v>65611</v>
+        <v>66996</v>
       </c>
       <c r="D32" t="n">
-        <v>1072</v>
+        <v>1112</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Обрешётка: □80×60×2 пл.; Стропила: □160×80×4; Затяжки: □60×40×2; Подвеска (стойка у конька): □50×25×2,1; Подкосы колонна→затяжка: □20×20×2; Колонны: □100×100×3,8</t>
+          <t>Колонны: □140×100×4; Связи по скатам: □90×30×2; Стропила: □160×80×4; Продольная обвязка: □35×35×2; Обрешётка: □60×60×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, попер. подкосы, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>202891</v>
+        <v>211326</v>
       </c>
       <c r="C33" t="n">
-        <v>62169</v>
+        <v>65578</v>
       </c>
       <c r="D33" t="n">
-        <v>1035</v>
+        <v>1062</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □120×80×3; Затяжки: □80×40×2,2 пл.; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Подкосы колонна→затяжка: □20×20×2; Подкосы фермы: □30×20×2; Продольная обвязка: □20×20×2; Колонны: □120×80×4</t>
+          <t>Продольные подкосы: □30×20×2; Колонны: □120×120×3; Связи по скатам: □90×30×2; Стропила: □160×80×4; Продольная обвязка: □30×20×2 пл.; Обрешётка: □60×60×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска, попер. подкосы, связи по скатам</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>203061</v>
+        <v>211849</v>
       </c>
       <c r="C34" t="n">
-        <v>57410</v>
+        <v>64254</v>
       </c>
       <c r="D34" t="n">
-        <v>1212</v>
+        <v>1057</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □100×100×4,8; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □80×40×2,2; Связи по скатам: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Продольная обвязка: □35×35×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □30×20×2; Колонны: □140×100×4; Связи по скатам: □70×70×2; Стропила: □120×80×3; Продольная обвязка: □35×35×2; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □30×20×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, попер. подкосы, без связей</t>
+          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, без попер. подкосов, связи по скатам</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>203980</v>
+        <v>212115</v>
       </c>
       <c r="C35" t="n">
-        <v>65424</v>
+        <v>66573</v>
       </c>
       <c r="D35" t="n">
-        <v>1077</v>
+        <v>1096</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Обрешётка: □80×60×2; Стропила: □160×80×4; Затяжки: □30×25×2; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Подкосы колонна→затяжка: □20×20×2; Продольная обвязка: □20×20×2; Колонны: □120×80×4</t>
+          <t>Подкосы фермы: □30×20×2; Колонны: □140×140×4; Связи по скатам: □80×80×2; Стропила: □120×80×3; Обрешётка: □60×60×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, попер. подкосы, связи по скатам</t>
+          <t>2 рамы (только по колоннам), обвязка, подвеска, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>204007</v>
+        <v>212534</v>
       </c>
       <c r="C36" t="n">
-        <v>56677</v>
+        <v>66836</v>
       </c>
       <c r="D36" t="n">
-        <v>1210</v>
+        <v>1111</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Обрешётка: □60×60×2,5; Стропила: □160×80×4; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Связи по скатам: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Продольная обвязка: □20×20×2; Колонны: □100×100×3,8</t>
+          <t>Колонны: □140×100×4; Связи по скатам: □90×30×2; Стропила: □160×80×4; Продольная обвязка: □35×35×2; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □30×20×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска, попер. подкосы, без связей</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>207210</v>
+        <v>212608</v>
       </c>
       <c r="C37" t="n">
-        <v>67676</v>
+        <v>65224</v>
       </c>
       <c r="D37" t="n">
-        <v>1521</v>
+        <v>1054</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Обрешётка: □80×80×3; Стропила: □160×80×4; Затяжки: □30×20×2; Подвеска (стойка у конька): □20×20×2; Подкосы колонна→затяжка: □20×20×2; Продольная обвязка: □35×35×2; Колонны: □120×80×4</t>
+          <t>Продольные подкосы: □30×20×2; Колонны: □120×120×3; Связи по скатам: □80×30×2; Стропила: □160×80×4; Продольная обвязка: □30×20×2 пл.; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □30×20×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
@@ -3680,80 +3727,80 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>212491</v>
+        <v>212658</v>
       </c>
       <c r="C38" t="n">
-        <v>68268</v>
+        <v>68904</v>
       </c>
       <c r="D38" t="n">
-        <v>1159</v>
+        <v>1136</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □100×100×4,8; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □80×40×2,2; Связи по скатам: □80×40×2,2; Колонны: □100×100×3,8</t>
+          <t>Колонны: □140×140×4; Связи по скатам: □80×80×2; Стропила: □120×80×4; Обрешётка: □60×60×2; Затяжки: □60×60×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка, подвеска, без попер. подкосов, связи по скатам</t>
+          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>214547</v>
+        <v>212770</v>
       </c>
       <c r="C39" t="n">
-        <v>68924</v>
+        <v>63146</v>
       </c>
       <c r="D39" t="n">
-        <v>1179</v>
+        <v>1019</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □160×80×4; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Связи по скатам: □80×40×2,2; Продольная обвязка: □35×35×2; Колонны: □100×100×3,8</t>
+          <t>Подкосы фермы: □30×20×2; Продольные подкосы: □25×25×2; Колонны: □100×100×3,8; Связи по скатам: □70×70×2; Стропила: □100×100×2,8; Продольная обвязка: □60×40×2; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □30×20×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □40×40×2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), подвеска, попер. подкосы, связи по скатам</t>
+          <t>2 рамы (только по колоннам), подвеска + подкосы фермы, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>214568</v>
+        <v>213997</v>
       </c>
       <c r="C40" t="n">
-        <v>68489</v>
+        <v>66492</v>
       </c>
       <c r="D40" t="n">
-        <v>1170</v>
+        <v>1096</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □100×100×4,8; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □80×40×2,2; Связи по скатам: □80×40×2,2; Подкосы колонна→затяжка: □20×20×2; Колонны: □120×80×4</t>
+          <t>Подкосы фермы: □30×20×2; Колонны: □140×140×4; Связи по скатам: □80×80×2; Стропила: □120×80×3; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □40×20×2; Затяжки: □40×40×2; Подвеска (стойка у конька): □20×20×2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2 рамы (только по колоннам), обвязка + прод. подкосы, подвеска, без попер. подкосов, связи по скатам</t>
+          <t>2 рамы (только по колоннам), подвеска, попер. подкосы, связи по скатам</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>215992</v>
+        <v>215202</v>
       </c>
       <c r="C41" t="n">
-        <v>68705</v>
+        <v>69149</v>
       </c>
       <c r="D41" t="n">
-        <v>1175</v>
+        <v>1138</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Обрешётка: □70×70×2; Стропила: □160×80×4; Затяжки: □80×40×2,2; Подвеска (стойка у конька): □20×20×2; Продольные подкосы: □20×20×2; Связи по скатам: □80×40×2,2; Продольная обвязка: □20×20×2; Колонны: □100×100×3,8</t>
+          <t>Колонны: □140×140×4; Связи по скатам: □80×80×2; Стропила: □120×80×4; Обрешётка: □60×60×2; Подкосы колонна→затяжка: □40×20×2; Затяжки: □50×50×2; Подвеска (стойка у конька): □50×50×2</t>
         </is>
       </c>
     </row>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76029</v>
+        <v>76057</v>
       </c>
       <c r="C2" t="n">
-        <v>44236</v>
+        <v>44252</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -959,7 +959,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1227 кг, стало 730 кг; площадь окраски 57.5 → 39.5 м²; швы 37.6 → 24.6 м; деталей 84 → 74.</t>
+          <t>Масса металла: было 1227 кг, стало 730 кг; площадь окраски 57.6 → 39.5 м²; швы 37.6 → 24.6 м; деталей 84 → 74.</t>
         </is>
       </c>
     </row>
@@ -1062,19 +1062,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.72</v>
+        <v>20.75</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>146.5</v>
+        <v>146.7</v>
       </c>
       <c r="F3" t="n">
         <v>428</v>
       </c>
       <c r="G3" t="n">
-        <v>8868</v>
+        <v>8879</v>
       </c>
     </row>
     <row r="4">
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26.25</v>
+        <v>26.27</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>226</v>
       </c>
       <c r="G5" t="n">
-        <v>5933</v>
+        <v>5937</v>
       </c>
     </row>
     <row r="6">
@@ -1155,7 +1155,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.706</v>
+        <v>3.71</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.195</v>
+        <v>3.199</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -1343,13 +1343,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.45</v>
+        <v>5.457</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.104</v>
+        <v>1.105</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.706</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.291</v>
+        <v>2.287</v>
       </c>
     </row>
     <row r="7">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.706</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.291</v>
+        <v>2.287</v>
       </c>
     </row>
     <row r="8">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.706</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.291</v>
+        <v>2.287</v>
       </c>
     </row>
     <row r="9">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.195</t>
+          <t>3.199</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.802</v>
+        <v>2.798</v>
       </c>
     </row>
     <row r="10">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.195</t>
+          <t>3.199</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.802</v>
+        <v>2.798</v>
       </c>
     </row>
     <row r="11">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.195</t>
+          <t>3.199</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.802</v>
+        <v>2.798</v>
       </c>
     </row>
     <row r="12">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.450</t>
+          <t>5.457</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.547</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="13">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.450</t>
+          <t>5.457</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.547</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="14">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.450</t>
+          <t>5.457</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.547</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="15">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.104 + 1.104 + 1.104 + 1.104 + 1.104</t>
+          <t>1.105 + 1.105 + 1.105 + 1.105 + 1.105</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.465</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="18">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.104 + 0.679 + 0.679 + 0.679</t>
+          <t>1.105 + 0.679 + 0.679 + 0.679</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.847</v>
+        <v>2.846</v>
       </c>
     </row>
     <row r="19">
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>24.01</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.488</v>
+        <v>2.477</v>
       </c>
       <c r="F2" t="n">
         <v>0.928</v>
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.11</v>
+        <v>28.14</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
         <v>4.066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.99</v>
+        <v>0.979</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="D4" t="n">
-        <v>26.39</v>
+        <v>26.41</v>
       </c>
       <c r="E4" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -2786,7 +2786,7 @@
         <v>5.63</v>
       </c>
       <c r="D6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="E6" t="n">
         <v>0.008999999999999999</v>
@@ -2841,13 +2841,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.81</v>
+        <v>19.83</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.183</v>
+        <v>0.185</v>
       </c>
       <c r="F8" t="n">
         <v>0.643</v>
@@ -2905,10 +2905,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.953</v>
+        <v>1.955</v>
       </c>
       <c r="F10" t="n">
-        <v>0.87</v>
+        <v>0.862</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -478,7 +478,7 @@
         <v>76057</v>
       </c>
       <c r="C2" t="n">
-        <v>44252</v>
+        <v>44542</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1522</v>
+        <v>1647</v>
       </c>
       <c r="C3" t="n">
-        <v>1249</v>
+        <v>1453</v>
       </c>
       <c r="D3">
         <f>C3-B3</f>
@@ -676,7 +676,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>3776</v>
+        <v>3807</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -698,7 +698,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>4323</v>
+        <v>4307</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -808,7 +808,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>17011</v>
+        <v>17003</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -830,7 +830,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>4806</v>
+        <v>4846</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -852,7 +852,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>10632</v>
+        <v>10627</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -918,7 +918,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>4961</v>
+        <v>4959</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -959,7 +959,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1227 кг, стало 730 кг; площадь окраски 57.6 → 39.5 м²; швы 37.6 → 24.6 м; деталей 84 → 74.</t>
+          <t>Масса металла: было 1230 кг, стало 744 кг; площадь окраски 57.6 → 39.9 м²; швы 37.6 → 24.5 м; деталей 84 → 74.</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×50×4</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1095,13 +1095,13 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>133.5</v>
+        <v>143.2</v>
       </c>
       <c r="F4" t="n">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="G4" t="n">
-        <v>8108</v>
+        <v>8387</v>
       </c>
     </row>
     <row r="5">
@@ -1161,7 +1161,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□70×70×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1176,13 +1176,13 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="F7" t="n">
-        <v>264</v>
+        <v>315</v>
       </c>
       <c r="G7" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -1207,7 +1207,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Пластины (фасонки, крышки колонн): 22.7 кг × 55 грн/кг</t>
+          <t>Пластины (фасонки, крышки колонн): 26.4 кг × 55 грн/кг</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>□100×50×4</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1283,7 +1283,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>133.4</v>
+        <v>143.1</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>□70×70×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1485,7 +1485,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr"/>
     </row>
@@ -1540,7 +1540,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>□100×50×4</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1563,7 +1563,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>□100×50×4</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1586,7 +1586,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×50×4</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1609,7 +1609,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□100×50×4</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2575,7 +2575,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>□70×70×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2663,20 +2663,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>□100×50×4</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.01</v>
+        <v>24.03</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.477</v>
+        <v>2.493</v>
       </c>
       <c r="F2" t="n">
-        <v>0.928</v>
+        <v>0.831</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2696,20 +2696,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.14</v>
+        <v>28.11</v>
       </c>
       <c r="D3" t="n">
         <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4.066</v>
+        <v>4.057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.979</v>
+        <v>0.951</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>устойчивость [D+S+0.9W+y]</t>
+          <t>устойчивость [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="D4" t="n">
-        <v>26.41</v>
+        <v>26.37</v>
       </c>
       <c r="E4" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -2760,10 +2760,10 @@
         <v>1.68</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2783,16 +2783,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="D6" t="n">
         <v>2.78</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.896</v>
+        <v>0.895</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="D7" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="E7" t="n">
         <v>0.438</v>
@@ -2841,13 +2841,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.83</v>
+        <v>19.93</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.185</v>
+        <v>0.183</v>
       </c>
       <c r="F8" t="n">
         <v>0.643</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>16.67</v>
+        <v>16.58</v>
       </c>
       <c r="E9" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="F9" t="n">
         <v>0.864</v>
@@ -2895,20 +2895,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□70×70×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.6</v>
+        <v>13.68</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.955</v>
+        <v>1.947</v>
       </c>
       <c r="F10" t="n">
-        <v>0.862</v>
+        <v>0.834</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76057</v>
+        <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>44542</v>
+        <v>44608</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -676,7 +676,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>3807</v>
+        <v>3813</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -808,7 +808,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>17003</v>
+        <v>17007</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -830,7 +830,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>4846</v>
+        <v>4853</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -852,7 +852,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>10627</v>
+        <v>10630</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -918,7 +918,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>4959</v>
+        <v>4960</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -959,7 +959,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1230 кг, стало 744 кг; площадь окраски 57.6 → 39.9 м²; швы 37.6 → 24.5 м; деталей 84 → 74.</t>
+          <t>Масса металла: было 1226 кг, стало 745 кг; площадь окраски 57.6 → 39.9 м²; швы 37.6 → 24.5 м; деталей 84 → 74.</t>
         </is>
       </c>
     </row>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.53</v>
+        <v>15.65</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>143.2</v>
+        <v>144.4</v>
       </c>
       <c r="F4" t="n">
         <v>540</v>
       </c>
       <c r="G4" t="n">
-        <v>8387</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="5">
@@ -1222,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1268,7 +1268,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Колонна П3 (верх бетона -0.27)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1277,217 +1277,283 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.88</v>
+        <v>4.013</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>143.1</v>
+        <v>37</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Колонна Л3 (верх бетона -0.25)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.71</v>
+        <v>3.993</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>78.7</v>
+        <v>36.8</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Колонна П1 (верх бетона -0.09)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.199</v>
+        <v>3.833</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>67.90000000000001</v>
+        <v>35.3</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Затяжки</t>
+          <t>Колонна Л1 (верх бетона -0.06)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.457</v>
+        <v>3.803</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>58.3</v>
+        <v>35.1</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька)</t>
+          <t>Стропила</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.679</v>
+        <v>3.71</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1</v>
+        <v>78.7</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Подкосы фермы</t>
+          <t>Стропила</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.105</v>
+        <v>3.199</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Затяжки</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.98</v>
+        <v>5.457</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>305.8</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>стык на раме: 2 заготовки</t>
-        </is>
-      </c>
+        <v>58.3</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Подвеска (стойка у конька)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.47</v>
+        <v>0.679</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>35.2</v>
+        <v>2.1</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Подкосы фермы</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.6</v>
+        <v>1.105</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>18.3</v>
+        <v>7</v>
       </c>
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Обрешётка</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="D11" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>305.8</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>стык на раме: 2 заготовки</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Раскосы боковой фермы</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Стойка-вставка средней рамы</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C14" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E14" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1548,16 +1614,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>4.013</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Колонна П3 (верх бетона -0.27)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.117</v>
+        <v>1.984</v>
       </c>
     </row>
     <row r="3">
@@ -1571,16 +1637,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.993</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Колонна Л3 (верх бетона -0.25)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.117</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="4">
@@ -1594,16 +1660,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.833</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Колонна П1 (верх бетона -0.09)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.117</v>
+        <v>2.164</v>
       </c>
     </row>
     <row r="5">
@@ -1617,16 +1683,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Колонна Л1 (верх бетона -0.06)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.117</v>
+        <v>2.194</v>
       </c>
     </row>
     <row r="6">
@@ -2667,20 +2733,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.03</v>
+        <v>24.06</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.493</v>
+        <v>2.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.831</v>
+        <v>0.849</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>гибкость [D+S]</t>
+          <t>гибкость [D+S+0.9W+y]</t>
         </is>
       </c>
     </row>
@@ -2702,10 +2768,10 @@
         <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4.057</v>
+        <v>4.063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.951</v>
+        <v>0.959</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2725,13 +2791,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="D4" t="n">
-        <v>26.37</v>
+        <v>26.38</v>
       </c>
       <c r="E4" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -2763,7 +2829,7 @@
         <v>0.021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2783,7 +2849,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="D6" t="n">
         <v>2.78</v>
@@ -2792,7 +2858,7 @@
         <v>0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.895</v>
+        <v>0.896</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2825,7 +2891,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>прочность [D+S+0.9W-x]</t>
+          <t>прочность [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
@@ -2841,13 +2907,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.93</v>
+        <v>19.95</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.183</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
         <v>0.643</v>
@@ -2873,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>16.58</v>
+        <v>16.68</v>
       </c>
       <c r="E9" t="n">
         <v>0.045</v>
@@ -2899,16 +2965,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.68</v>
+        <v>13.67</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.947</v>
+        <v>1.946</v>
       </c>
       <c r="F10" t="n">
-        <v>0.834</v>
+        <v>0.836</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -11,9 +11,10 @@
     <sheet name="Ведомость металла" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Детали" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Раскрой (хлыст 6 м)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Проверки" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Варианты схем" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Нагрузки" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Пластины" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Проверки" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Варианты схем" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Нагрузки" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1222,21 +1223,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Деталь</t>
+          <t>Заготовка</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1246,7 +1247,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Длина, м</t>
+          <t>Длина реза, м</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1261,14 +1262,14 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Примечание</t>
+          <t>Торцы</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Колонна П3 (верх бетона -0.27)</t>
+          <t>Колонна Л1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1277,20 +1278,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.013</v>
+        <v>3.803</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>35.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Колонна Л3 (верх бетона -0.25)</t>
+          <t>Колонна Л3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1307,12 +1312,16 @@
       <c r="E3" t="n">
         <v>36.8</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Колонна П1 (верх бетона -0.09)</t>
+          <t>Колонна П1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1329,12 +1338,16 @@
       <c r="E4" t="n">
         <v>35.3</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Колонна Л1 (верх бетона -0.06)</t>
+          <t>Колонна П3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1343,20 +1356,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.803</v>
+        <v>4.013</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1373,12 +1390,16 @@
       <c r="E6" t="n">
         <v>78.7</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>у конька — вертикальный рез (78° к оси), у карниза — перпендикулярно оси</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1395,12 +1416,16 @@
       <c r="E7" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>у конька — вертикальный рез (78° к оси), у карниза — перпендикулярно оси</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Затяжки</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1409,42 +1434,50 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.457</v>
+        <v>5.357</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>38.2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>оба торца — прямые, между гранями колонн</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька)</t>
+          <t>Затяжка средней рамы</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.679</v>
+        <v>5.397</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>оба торца — прямые, между гранями стоек</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Подкосы фермы</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1453,68 +1486,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.105</v>
+        <v>0.598</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>низ — прямой, верх — «домиком» 2×12° под стропила</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.98</v>
+        <v>0.95</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>305.8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>стык на раме: 2 заготовки</t>
+          <t>низ — под 25° к оси (на затяжку у подвески), верх — под 37° (на стропило)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.47</v>
+        <v>5.78</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>253.2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>торцы прямые; стык с частью 2 — над стропилом рамы 3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1523,37 +1564,97 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>52.6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>торцы прямые</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>оба торца — вертикальные резы (69.7° к оси)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>оба торца — прямые, между гранями колонн</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Стойка-вставка</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C16" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="D16" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>низ — прямой (+ заглушка), верх — под 12°</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1566,13 +1667,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1594,7 +1695,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Детали</t>
+          <t>Заготовки</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1619,7 +1720,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Колонна П3 (верх бетона -0.27)</t>
+          <t>Колонна П3</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1642,7 +1743,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Колонна Л3 (верх бетона -0.25)</t>
+          <t>Колонна Л3</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1665,7 +1766,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Колонна П1 (верх бетона -0.09)</t>
+          <t>Колонна П1</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1688,7 +1789,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Колонна Л1 (верх бетона -0.06)</t>
+          <t>Колонна Л1</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1711,7 +1812,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1734,7 +1835,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1757,7 +1858,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1780,7 +1881,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1803,7 +1904,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1826,7 +1927,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1844,16 +1945,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.457</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Затяжки</t>
+          <t>Затяжка средней рамы</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -1867,16 +1968,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.457</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Затяжки</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="14">
@@ -1890,16 +1991,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.457</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Затяжки</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="15">
@@ -1913,16 +2014,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.470 + 2.470</t>
+          <t>2.383 + 2.383</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.054</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="16">
@@ -1936,16 +2037,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.470 + 2.470</t>
+          <t>2.383 + 2.383</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.054</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="17">
@@ -1959,16 +2060,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.105 + 1.105 + 1.105 + 1.105 + 1.105</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Подкосы фермы</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.46</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="18">
@@ -1982,16 +2083,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.105 + 0.679 + 0.679 + 0.679</t>
+          <t>0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька); Подкосы фермы</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.846</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="19">
@@ -2005,16 +2106,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="20">
@@ -2028,16 +2129,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="21">
@@ -2051,16 +2152,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="22">
@@ -2074,16 +2175,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="23">
@@ -2097,16 +2198,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="24">
@@ -2120,16 +2221,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="25">
@@ -2143,16 +2244,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="26">
@@ -2166,16 +2267,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="27">
@@ -2189,16 +2290,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="28">
@@ -2212,16 +2313,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="29">
@@ -2235,16 +2336,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="30">
@@ -2258,16 +2359,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="31">
@@ -2281,16 +2382,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="32">
@@ -2304,16 +2405,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="33">
@@ -2327,16 +2428,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="34">
@@ -2350,16 +2451,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="35">
@@ -2373,16 +2474,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="36">
@@ -2396,16 +2497,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="37">
@@ -2419,16 +2520,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="38">
@@ -2442,16 +2543,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="39">
@@ -2465,16 +2566,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="40">
@@ -2488,16 +2589,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Обрешётка (часть)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-0.003</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="41">
@@ -2511,16 +2612,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4.600 + 0.980</t>
+          <t>4.540 + 1.200</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы; Обрешётка</t>
+          <t>Нижний пояс боковой фермы; Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.414</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="42">
@@ -2534,16 +2635,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4.600 + 0.980</t>
+          <t>4.540 + 1.200</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы; Обрешётка</t>
+          <t>Нижний пояс боковой фермы; Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.414</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="43">
@@ -2557,16 +2658,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
+          <t>1.200 + 1.200 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.102</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="44">
@@ -2580,16 +2681,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
+          <t>1.200 + 1.200 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.102</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="45">
@@ -2603,16 +2704,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.980 + 0.980 + 0.980 + 0.980 + 0.980 + 0.980</t>
+          <t>1.200 + 1.200 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.102</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="46">
@@ -2626,39 +2727,62 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.980 + 0.980</t>
+          <t>1.200 + 1.200 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.034</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>29</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.200 + 1.200 + 1.200 + 1.200</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1.188</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B48" t="n">
         <v>1</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0.100 + 0.100</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Стойка-вставка средней рамы</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>5.794</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.113 + 0.113</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Стойка-вставка</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5.768</v>
       </c>
     </row>
   </sheetData>
@@ -2667,6 +2791,254 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Размер, мм</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>t, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Масса, кг</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Где</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Из чего резать</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Фасонка</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>трапеция 250 × 169 / 223</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>узлы А (4 × 2) и Б (2 × 2)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>полоса 250 мм из листа t=5: 6 пар «валетом» по 392 мм → 250 × 2352</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Опорная пластина под стропило</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>140 × 60</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>верх колонн и стоек-вставок</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>полоса 60×6: 6 × 140 = 840 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Заглушка низа колонны</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>110 × 70</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>низ колонн в лунке</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>лист t=4: 4 шт → 220 × 140</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Заглушка низа стойки-вставки</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>60 × 60</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>узел Б</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>полоса 60×3: 2 × 60 = 120 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Заглушка торца стропила в свесе</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100 × 60</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>концы стропил у карниза</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>лист t=2 (или пластиковые заглушки 100×60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Заглушка торца обрешётины</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>35 × 35</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>торцы обрешётин на кромках кровли</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>пластиковые заглушки 35×35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2987,7 +3359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3875,7 +4247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Ведомость металла" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Детали" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Раскрой (хлыст 6 м)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Раскрой (хлысты 6 и 12 м)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Пластины" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Проверки" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Варианты схем" sheetId="7" state="visible" r:id="rId7"/>
@@ -479,7 +479,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>44608</v>
+        <v>44600</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -699,7 +699,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>4307</v>
+        <v>3792</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -809,7 +809,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>17007</v>
+        <v>13799</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -853,7 +853,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>10630</v>
+        <v>8625</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -919,7 +919,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>4960</v>
+        <v>4025</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -960,7 +960,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 745 кг; площадь окраски 57.6 → 39.9 м²; швы 37.6 → 24.5 м; деталей 84 → 74.</t>
+          <t>Масса металла: было 1226 кг, стало 745 кг; площадь окраски 57.6 → 39.9 м²; швы 37.6 → 21.6 м; деталей 84 → 52.</t>
         </is>
       </c>
     </row>
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>162.9</v>
+        <v>162.83</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>324.4</v>
+        <v>324.3</v>
       </c>
       <c r="F2" t="n">
         <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>20688</v>
+        <v>20680</v>
       </c>
     </row>
     <row r="3">
@@ -1223,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1529,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Обрешётина цельная</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1538,119 +1538,93 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.78</v>
+        <v>6.98</v>
       </c>
       <c r="D12" t="n">
         <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>253.2</v>
+        <v>305.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>торцы прямые; стык с частью 2 — над стропилом рамы 3</t>
+          <t>торцы прямые; из хлыста 12 м, без стыка</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.2</v>
+        <v>2.383</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>52.6</v>
+        <v>33.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>торцы прямые</t>
+          <t>оба торца — вертикальные резы (69.7° к оси)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.383</v>
+        <v>4.54</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>33.9</v>
+        <v>18.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>оба торца — вертикальные резы (69.7° к оси)</t>
+          <t>оба торца — прямые, между гранями колонн</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Стойка-вставка</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.54</v>
+        <v>0.113</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>оба торца — прямые, между гранями колонн</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Стойка-вставка</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>□60×60×3</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>низ — прямой (+ заглушка), верх — под 12°</t>
         </is>
@@ -1667,7 +1641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1710,21 +1684,23 @@
           <t>□100×60×4</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1 (12 м)</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.013</t>
+          <t>4.013 + 3.993 + 3.833</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Колонна П3</t>
+          <t>Колонна Л3; Колонна П1; Колонна П3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.984</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="3">
@@ -1733,366 +1709,398 @@
           <t>□100×60×4</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2 (6 м)</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.993</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Колонна Л3</t>
+          <t>Колонна Л1</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.004</v>
+        <v>2.194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>□100×60×3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1 (12 м)</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>3.710 + 3.710 + 3.710</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Колонна П1</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.164</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+          <t>□100×60×3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2 (12 м)</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.803</t>
+          <t>3.199 + 3.199 + 3.199</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Колонна Л1</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.194</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1 (12 м)</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>5.397 + 5.357</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Затяжка крайней рамы; Затяжка средней рамы</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.287</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2 (12 м)</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>5.357 + 2.383 + 2.383</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Затяжка крайней рамы; Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.287</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3 (6 м)</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>2.383 + 2.383</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.287</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
+          <t>□20×20×2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1 (12 м)</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Подвеска у конька; Подкос фермы</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.798</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1 (12 м)</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.798</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2 (12 м)</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.798</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3 (12 м)</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.397</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Затяжка средней рамы</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4 (12 м)</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.64</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5 (12 м)</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.64</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6 (12 м)</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.383 + 2.383</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.228</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7 (12 м)</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.383 + 2.383</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.228</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8 (12 м)</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Подкос фермы</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.282</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9 (12 м)</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Подвеска у конька</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.197</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="19">
@@ -2101,12 +2109,14 @@
           <t>□35×35×2</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10 (12 м)</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2115,7 +2125,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.217</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="20">
@@ -2124,12 +2134,14 @@
           <t>□35×35×2</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>2</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11 (12 м)</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2138,7 +2150,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.217</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="21">
@@ -2147,21 +2159,23 @@
           <t>□35×35×2</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>3</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12 (12 м)</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>4.540 + 4.540 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Нижний пояс боковой фермы; Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.217</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="22">
@@ -2170,21 +2184,23 @@
           <t>□35×35×2</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>4</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13 (12 м)</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.217</v>
+        <v>1.173</v>
       </c>
     </row>
     <row r="23">
@@ -2193,21 +2209,23 @@
           <t>□35×35×2</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>5</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14 (12 м)</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.217</v>
+        <v>1.173</v>
       </c>
     </row>
     <row r="24">
@@ -2216,572 +2234,47 @@
           <t>□35×35×2</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>6</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>15 (6 м)</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>1.200 + 1.200</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Обрешётина, часть 2 (рама 3 → край)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.217</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>7</v>
+          <t>□60×60×3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1 (6 м)</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>0.113 + 0.113</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Стойка-вставка</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>8</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>9</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>10</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>11</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>12</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>13</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>14</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>15</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>16</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>17</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>18</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>19</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>20</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>21</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>22</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>23</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>4.540 + 1.200</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Нижний пояс боковой фермы; Обрешётина, часть 2 (рама 3 → край)</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0.254</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>24</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>4.540 + 1.200</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Нижний пояс боковой фермы; Обрешётина, часть 2 (рама 3 → край)</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>0.254</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>25</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1.188</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>26</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1.188</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>27</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1.188</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>28</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1.188</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>29</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1.188</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>□60×60×3</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0.113 + 0.113</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Стойка-вставка</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
         <v>5.768</v>
       </c>
     </row>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -11,10 +11,11 @@
     <sheet name="Ведомость металла" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Детали" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Раскрой (хлысты 6 и 12 м)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Пластины" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Проверки" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Варианты схем" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Нагрузки" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Металлочерепица" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Пластины" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Проверки" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Варианты схем" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Нагрузки" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2289,6 +2290,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Скат</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Лист №</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Длина листа, м</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Полезн. ширина у карниза, мм</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>у конька, мм</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Подрезка (у карниза → у конька)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Левый скат (свес 0.40 м)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>943</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>передняя кромка 0→157 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Левый скат (свес 0.40 м)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Левый скат (свес 0.40 м)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Левый скат (свес 0.40 м)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Левый скат (свес 0.40 м)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Левый скат (свес 0.40 м)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Левый скат (свес 0.40 м)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D8" t="n">
+        <v>380</v>
+      </c>
+      <c r="E8" t="n">
+        <v>537</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>задняя кромка 720→562 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Правый скат (свес 0.90 м)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="D9" t="n">
+        <v>918</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>передняя кромка 182→0 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Правый скат (свес 0.90 м)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Правый скат (свес 0.90 м)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Правый скат (свес 0.90 м)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Правый скат (свес 0.90 м)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Правый скат (свес 0.90 м)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Правый скат (свес 0.90 м)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="D15" t="n">
+        <v>562</v>
+      </c>
+      <c r="E15" t="n">
+        <v>380</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>задняя кромка 537→720 мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Итого 14 листов; площадь по габаритной ширине 1.18 м — 57.2 м², по полезной — 53.4 м²; кровля 48.2 м². Укладка от переднего края (дорога).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2531,7 +2929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2852,7 +3250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3740,7 +4138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>44600</v>
+        <v>45525</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -502,7 +502,7 @@
         <v>1647</v>
       </c>
       <c r="C3" t="n">
-        <v>1453</v>
+        <v>1658</v>
       </c>
       <c r="D3">
         <f>C3-B3</f>
@@ -678,7 +678,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>3813</v>
+        <v>3911</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -700,7 +700,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>3792</v>
+        <v>3862</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>13799</v>
+        <v>13913</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -832,7 +832,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>4853</v>
+        <v>4977</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>8625</v>
+        <v>8695</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>4025</v>
+        <v>4058</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 745 кг; площадь окраски 57.6 → 39.9 м²; швы 37.6 → 21.6 м; деталей 84 → 52.</t>
+          <t>Масса металла: было 1226 кг, стало 763 кг; площадь окраски 57.6 → 40.9 м²; швы 37.6 → 22.0 м; деталей 84 → 52.</t>
         </is>
       </c>
     </row>
@@ -1033,23 +1033,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы, Обрешётка</t>
+          <t>Обрешётка</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>162.83</v>
+        <v>153.63</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>324.3</v>
+        <v>306</v>
       </c>
       <c r="F2" t="n">
         <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>20680</v>
+        <v>19511</v>
       </c>
     </row>
     <row r="3">
@@ -1114,23 +1114,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Затяжки, Раскосы боковой фермы</t>
+          <t>Затяжки, Нижний пояс боковой фермы, Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26.27</v>
+        <v>35.41</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>93.59999999999999</v>
+        <v>126.1</v>
       </c>
       <c r="F5" t="n">
         <v>226</v>
       </c>
       <c r="G5" t="n">
-        <v>5937</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="6">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="F7" t="n">
         <v>315</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -1209,7 +1209,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Пластины (фасонки, крышки колонн): 26.4 кг × 55 грн/кг</t>
+          <t>Пластины (фасонки, крышки колонн): 30.1 кг × 55 грн/кг</t>
         </is>
       </c>
     </row>
@@ -1565,17 +1565,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.383</v>
+        <v>2.403</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>оба торца — вертикальные резы (69.7° к оси)</t>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1597,11 +1597,11 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>18.1</v>
+        <v>32.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>оба торца — прямые, между гранями колонн</t>
+          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>низ — прямой (+ заглушка), верх — под 12°</t>
+          <t>низ — прямой (встаёт на столик фермы), верх — под 12°</t>
         </is>
       </c>
     </row>
@@ -1817,16 +1817,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.357 + 2.383 + 2.383</t>
+          <t>5.357 + 4.540</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы; Раскос боковой фермы</t>
+          <t>Затяжка крайней рамы; Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.868</v>
+        <v>2.097</v>
       </c>
     </row>
     <row r="8">
@@ -1837,52 +1837,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>3 (12 м)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.383 + 2.383</t>
+          <t>4.540 + 2.403 + 2.403 + 2.403</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Нижний пояс боковой фермы; Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.228</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.598 + 0.598 + 0.598</t>
+          <t>2.403</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Подвеска у конька; Подкос фермы</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.479</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1892,16 +1892,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Подвеска у конька; Подкос фермы</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.434</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="11">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
+          <t>1 (12 м)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3 (12 м)</t>
+          <t>2 (12 м)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4 (12 м)</t>
+          <t>3 (12 м)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5 (12 м)</t>
+          <t>4 (12 м)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6 (12 м)</t>
+          <t>5 (12 м)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7 (12 м)</t>
+          <t>6 (12 м)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8 (12 м)</t>
+          <t>7 (12 м)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9 (12 м)</t>
+          <t>8 (12 м)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10 (12 м)</t>
+          <t>9 (12 м)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11 (12 м)</t>
+          <t>10 (12 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2162,21 +2162,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12 (12 м)</t>
+          <t>11 (12 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.540 + 4.540 + 1.200 + 1.200</t>
+          <t>5.780 + 5.780</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы; Обрешётина, часть 2 (рама 3 → край)</t>
+          <t>Обрешётина, часть 1 (край → рама 3)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.508</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="22">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13 (12 м)</t>
+          <t>12 (12 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14 (12 м)</t>
+          <t>13 (12 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15 (6 м)</t>
+          <t>14 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.200 + 1.200</t>
+          <t>1.200 + 1.200 + 1.200 + 1.200</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.594</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="25">
@@ -2687,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2739,7 +2739,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Фасонка</t>
+          <t>Фасонка узла А</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2751,174 +2751,205 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>23.08</v>
+        <v>15.39</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>узлы А (4 × 2) и Б (2 × 2)</t>
+          <t>узлы А (4 × 2), ставятся на объекте</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>полоса 250 мм из листа t=5: 6 пар «валетом» по 392 мм → 250 × 2352</t>
+          <t>полоса 250 мм из листа t=5: 4 пары «валетом» по 392 мм → 250 × 1568</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Опорная пластина под стропило</t>
+          <t>Фасонка узла Б</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>140 × 60</t>
+          <t>трапеция 230 × 164 / 213</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2.37</v>
+        <v>6.79</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>верх колонн и стоек-вставок</t>
+          <t>узлы Б (2 × 2), в цеху на средней раме</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>полоса 60×6: 6 × 140 = 840 мм</t>
+          <t>полоса 230 мм из листа t=5: 2 пары «валетом» по 377 мм → 230 × 754</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Заглушка низа колонны</t>
+          <t>Опорный столик боковой фермы</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>110 × 70</t>
+          <t>370 × 80</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.97</v>
+        <v>3.72</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>низ колонн в лунке</t>
+          <t>вершина боковой фермы</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>лист t=4: 4 шт → 220 × 140</t>
+          <t>полоса 80×8: 2 × 370 = 740 мм</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Заглушка низа стойки-вставки</t>
+          <t>Опорная пластина под стропило</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60 × 60</t>
+          <t>140 × 60</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>2.37</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>узел Б</t>
+          <t>верх колонн и стоек-вставок</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>полоса 60×3: 2 × 60 = 120 мм</t>
+          <t>полоса 60×6: 6 × 140 = 840 мм</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Заглушка торца стропила в свесе</t>
+          <t>Заглушка низа колонны</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100 × 60</t>
+          <t>110 × 70</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.57</v>
+        <v>0.97</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>концы стропил у карниза</t>
+          <t>низ колонн в лунке</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>лист t=2 (или пластиковые заглушки 100×60)</t>
+          <t>лист t=4: 4 шт → 220 × 140</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Заглушка торца стропила в свесе</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>100 × 60</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>концы стропил у карниза</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>лист t=2 (или пластиковые заглушки 100×60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Заглушка торца обрешётины</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>35 × 35</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>44</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>торцы обрешётин на кромках кровли</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>пластиковые заглушки 35×35</t>
         </is>
@@ -2996,20 +3027,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.06</v>
+        <v>24.1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2.511</v>
       </c>
       <c r="F2" t="n">
-        <v>0.849</v>
+        <v>0.857</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>гибкость [D+S+0.9W+y]</t>
+          <t>гибкость [D+S]</t>
         </is>
       </c>
     </row>
@@ -3025,13 +3056,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.11</v>
+        <v>28.09</v>
       </c>
       <c r="D3" t="n">
         <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4.063</v>
+        <v>4.073</v>
       </c>
       <c r="F3" t="n">
         <v>0.959</v>
@@ -3054,13 +3085,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="D4" t="n">
-        <v>26.38</v>
+        <v>26.35</v>
       </c>
       <c r="E4" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -3141,10 +3172,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="E7" t="n">
         <v>0.438</v>
@@ -3170,13 +3201,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.95</v>
+        <v>20.87</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18</v>
+        <v>0.166</v>
       </c>
       <c r="F8" t="n">
         <v>0.643</v>
@@ -3195,24 +3226,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>16.68</v>
+        <v>17.85</v>
       </c>
       <c r="E9" t="n">
-        <v>0.045</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>0.864</v>
+        <v>0.643</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>гибкость раст. [D+S]</t>
+          <t>стенка c/t изг. [D+S]</t>
         </is>
       </c>
     </row>
@@ -3228,20 +3259,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.67</v>
+        <v>13.97</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.946</v>
+        <v>1.95</v>
       </c>
       <c r="F10" t="n">
-        <v>0.836</v>
+        <v>0.83</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>устойчивость [D+S+0.9W+y]</t>
+          <t>устойчивость [D+S]</t>
         </is>
       </c>
     </row>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Ведомость металла" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Детали" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Раскрой (хлысты 6 и 12 м)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Раскрой на хлысты" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Металлочерепица" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Пластины" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Проверки" sheetId="7" state="visible" r:id="rId7"/>
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>45525</v>
+        <v>45534</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -700,7 +700,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>3862</v>
+        <v>4377</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>13913</v>
+        <v>17121</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>8695</v>
+        <v>10700</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>4058</v>
+        <v>4993</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 763 кг; площадь окраски 57.6 → 40.9 м²; швы 37.6 → 22.0 м; деталей 84 → 52.</t>
+          <t>Масса металла: было 1226 кг, стало 763 кг; площадь окраски 57.6 → 40.9 м²; швы 37.6 → 24.9 м; деталей 84 → 74.</t>
         </is>
       </c>
     </row>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>153.63</v>
+        <v>153.69</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>306</v>
+        <v>306.1</v>
       </c>
       <c r="F2" t="n">
         <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>19511</v>
+        <v>19519</v>
       </c>
     </row>
     <row r="3">
@@ -1224,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1530,102 +1530,154 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Обрешётина цельная</t>
+          <t>Вкладыш стыка обрешётины</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.98</v>
+        <v>0.1</v>
       </c>
       <c r="D12" t="n">
         <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>305.8</v>
+        <v>3.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>торцы прямые; из хлыста 12 м, без стыка</t>
+          <t>отрезок трубы внутрь стыка, по 50 мм в каждую часть</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.403</v>
+        <v>5.49</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>34.2</v>
+        <v>240.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (на вкладыше, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.54</v>
+        <v>1.49</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>32.3</v>
+        <v>65.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+          <t>торцы прямые</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Раскос боковой фермы</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2.403</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Стойка-вставка</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C17" t="n">
         <v>0.113</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E17" t="n">
         <v>1.2</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>низ — прямой (встаёт на столик фермы), верх — под 12°</t>
         </is>
@@ -1642,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1687,21 +1739,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.013 + 3.993 + 3.833</t>
+          <t>4.013</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Колонна Л3; Колонна П1; Колонна П3</t>
+          <t>Колонна П3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.152</v>
+        <v>1.984</v>
       </c>
     </row>
     <row r="3">
@@ -1717,147 +1769,147 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.803</t>
+          <t>3.993</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Колонна Л1</t>
+          <t>Колонна Л3</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.194</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.710 + 3.710 + 3.710</t>
+          <t>3.833</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Колонна П1</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.861</v>
+        <v>2.164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.199 + 3.199 + 3.199</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Колонна Л1</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.394</v>
+        <v>2.194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.397 + 5.357</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы; Затяжка средней рамы</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.24</v>
+        <v>2.287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.357 + 4.540</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы; Нижний пояс боковой фермы</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.097</v>
+        <v>2.287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3 (12 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.540 + 2.403 + 2.403 + 2.403</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы; Раскос боковой фермы</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.239</v>
+        <v>2.287</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1867,316 +1919,316 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.403</t>
+          <t>3.199</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.594</v>
+        <v>2.798</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.598 + 0.598 + 0.598</t>
+          <t>3.199</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Подвеска у конька; Подкос фермы</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.479</v>
+        <v>2.798</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>3.199</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.434</v>
+        <v>2.798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Затяжка средней рамы</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.434</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3 (12 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.434</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4 (12 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.434</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5 (12 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.434</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6 (12 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.434</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7 (12 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.434</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8 (12 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.434</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9 (12 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.434</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10 (12 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.434</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11 (12 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.780 + 5.780</t>
+          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (край → рама 3)</t>
+          <t>Вкладыш стыка обрешётины</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.434</v>
+        <v>3.734</v>
       </c>
     </row>
     <row r="22">
@@ -2187,21 +2239,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12 (12 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.173</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="23">
@@ -2212,21 +2264,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13 (12 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200 + 1.200</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.173</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="24">
@@ -2237,45 +2289,670 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.200 + 1.200 + 1.200 + 1.200</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (рама 3 → край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.188</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4 (6 м)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5 (6 м)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6 (6 м)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7 (6 м)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>8 (6 м)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>9 (6 м)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10 (6 м)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11 (6 м)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12 (6 м)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>13 (6 м)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14 (6 м)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15 (6 м)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16 (6 м)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17 (6 м)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>18 (6 м)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>19 (6 м)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20 (6 м)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21 (6 м)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>22 (6 м)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5.490</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>23 (6 м)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>24 (6 м)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>25 (6 м)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>26 (6 м)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>27 (6 м)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>28 (6 м)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3.014</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>1 (6 м)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>0.113 + 0.113</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Стойка-вставка</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E50" t="n">
         <v>5.768</v>
       </c>
     </row>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -1694,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1739,21 +1739,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>1 (12 м)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.013</t>
+          <t>4.013 + 3.993 + 3.833</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Колонна П3</t>
+          <t>Колонна Л3; Колонна П1; Колонна П3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.984</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="3">
@@ -1764,77 +1764,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>2 (12 м)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.993</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Колонна Л3</t>
+          <t>Колонна Л1</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.004</v>
+        <v>8.194000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>1 (12 м)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>3.710 + 3.710 + 3.710</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Колонна П1</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.164</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>2 (12 м)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.803</t>
+          <t>3.199 + 3.199 + 3.199</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Колонна Л1</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.194</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1844,22 +1844,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Затяжка средней рамы</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.287</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1869,22 +1869,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.287</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.287</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1919,22 +1919,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.798</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1944,22 +1944,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.798</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1969,16 +1969,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.798</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="12">
@@ -1989,246 +1989,246 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.397</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Затяжка средней рамы</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.64</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.64</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Вкладыш стыка обрешётины</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.457</v>
+        <v>3.734</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.457</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.188</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.188</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Подкос фермы</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.282</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Подвеска у конька</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.197</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.734</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="22">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>8 (6 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>9 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>10 (6 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>11 (6 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>12 (6 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>13 (6 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8 (6 м)</t>
+          <t>14 (6 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9 (6 м)</t>
+          <t>15 (6 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10 (6 м)</t>
+          <t>16 (6 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11 (6 м)</t>
+          <t>17 (6 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12 (6 м)</t>
+          <t>18 (6 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13 (6 м)</t>
+          <t>19 (6 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14 (6 м)</t>
+          <t>20 (6 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15 (6 м)</t>
+          <t>21 (6 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16 (6 м)</t>
+          <t>22 (6 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,21 +2639,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17 (6 м)</t>
+          <t>23 (6 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="39">
@@ -2664,21 +2664,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18 (6 м)</t>
+          <t>24 (6 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="40">
@@ -2689,21 +2689,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19 (6 м)</t>
+          <t>25 (6 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="41">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20 (6 м)</t>
+          <t>26 (6 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="42">
@@ -2739,21 +2739,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21 (6 м)</t>
+          <t>27 (6 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="43">
@@ -2764,195 +2764,45 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22 (6 м)</t>
+          <t>28 (6 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.507</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>23 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>0.113 + 0.113</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Стойка-вставка</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>24 (6 м)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>25 (6 м)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>26 (6 м)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>27 (6 м)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>□35×35×2</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>28 (6 м)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1.490 + 1.490</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>3.014</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>□60×60×3</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1 (6 м)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0.113 + 0.113</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Стойка-вставка</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
         <v>5.768</v>
       </c>
     </row>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>45534</v>
+        <v>49265</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -678,7 +678,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>3911</v>
+        <v>4279</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -700,7 +700,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>4377</v>
+        <v>5481</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>17121</v>
+        <v>21216</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -832,7 +832,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>4977</v>
+        <v>5446</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>10700</v>
+        <v>13260</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>4993</v>
+        <v>6188</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 763 кг; площадь окраски 57.6 → 40.9 м²; швы 37.6 → 24.9 м; деталей 84 → 74.</t>
+          <t>Масса металла: было 1226 кг, стало 822 кг; площадь окраски 57.6 → 44.8 м²; швы 37.6 → 31.2 м; деталей 84 → 82.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1055,159 +1055,186 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Затяжки, Нижний пояс боковой фермы, Раскосы боковой фермы, Торцевая обвязка обрешётки</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.75</v>
+        <v>49.19</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>146.7</v>
+        <v>175.2</v>
       </c>
       <c r="F3" t="n">
-        <v>428</v>
+        <v>226</v>
       </c>
       <c r="G3" t="n">
-        <v>8879</v>
+        <v>11117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Стропила</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.65</v>
+        <v>20.75</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>144.4</v>
+        <v>146.7</v>
       </c>
       <c r="F4" t="n">
-        <v>540</v>
+        <v>428</v>
       </c>
       <c r="G4" t="n">
-        <v>8453</v>
+        <v>8879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Затяжки, Нижний пояс боковой фермы, Раскосы боковой фермы</t>
+          <t>Колонны</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.41</v>
+        <v>15.65</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>126.1</v>
+        <v>144.4</v>
       </c>
       <c r="F5" t="n">
-        <v>226</v>
+        <v>540</v>
       </c>
       <c r="G5" t="n">
-        <v>8003</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька), Подкосы фермы</t>
+          <t>Подкосы торцевой обвязки</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.69</v>
+        <v>5.71</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="F6" t="n">
-        <v>67.40000000000001</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>586</v>
+        <v>617</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы</t>
+          <t>Подвеска (стойка у конька), Подкосы фермы</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3</v>
+        <v>8.69</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>9.1</v>
       </c>
       <c r="F7" t="n">
-        <v>315</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ИТОГО трубы</t>
-        </is>
-      </c>
-      <c r="C8">
-        <f>SUM(C2:C7)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>SUM(G2:G7)</f>
-        <v/>
+          <t>□60×60×3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Стойка-вставка средней рамы</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>315</v>
+      </c>
+      <c r="G8" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>ИТОГО трубы</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUM(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUM(G2:G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Пластины (фасонки, крышки колонн): 30.1 кг × 55 грн/кг</t>
         </is>
@@ -1224,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1608,7 +1635,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1617,24 +1644,24 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.403</v>
+        <v>3.698</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>34.2</v>
+        <v>26.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+          <t>у карниза — прямой рез, у конька — вертикальный рез (78° к оси) встык со второй половиной</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1643,41 +1670,145 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.54</v>
+        <v>3.186</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>32.3</v>
+        <v>22.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+          <t>у карниза — прямой рез, у конька — вертикальный рез (78° к оси) встык со второй половиной</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Стойка-вставка</t>
+          <t>Подкос торцевой обвязки, задний свес</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.113</v>
+        <v>1.362</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>низ — вертикальный рез к грани колонны на +2.10, верх — горизонтальный рез под обвязку (45° к горизонту)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Подкос торцевой обвязки, передний свес</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>□30×30×2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>низ — вертикальный рез к грани колонны на +2.10, верх — горизонтальный рез под обвязку (45° к горизонту)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Раскос боковой фермы</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.403</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Стойка-вставка</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>□60×60×3</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
         <v>1.2</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>низ — прямой (встаёт на столик фермы), верх — под 12°</t>
         </is>
@@ -1694,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1969,16 +2100,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>3.698</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.188</v>
+        <v>2.299</v>
       </c>
     </row>
     <row r="12">
@@ -1994,97 +2125,97 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>3.698</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.188</v>
+        <v>2.299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>8 (6 м)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
+          <t>3.186 + 2.403</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Подкос фермы</t>
+          <t>Раскос боковой фермы; Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.282</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>9 (6 м)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598</t>
+          <t>3.186 + 2.403</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Подвеска у конька</t>
+          <t>Раскос боковой фермы; Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.197</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>10 (6 м)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.734</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2094,22 +2225,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.507</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2119,66 +2250,66 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.507</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.362 + 1.362 + 1.348 + 1.348 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Вкладыш стыка обрешётины; Подкос торцевой обвязки, задний свес; Подкос торцевой обвязки, передний свес</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.507</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Вкладыш стыка обрешётины</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.507</v>
+        <v>4.249</v>
       </c>
     </row>
     <row r="20">
@@ -2189,7 +2320,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2214,7 +2345,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2239,7 +2370,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2264,7 +2395,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2289,7 +2420,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2314,7 +2445,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2339,7 +2470,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2364,7 +2495,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12 (6 м)</t>
+          <t>8 (6 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2389,7 +2520,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13 (6 м)</t>
+          <t>9 (6 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2414,7 +2545,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14 (6 м)</t>
+          <t>10 (6 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2439,7 +2570,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15 (6 м)</t>
+          <t>11 (6 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2464,7 +2595,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16 (6 м)</t>
+          <t>12 (6 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2489,7 +2620,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17 (6 м)</t>
+          <t>13 (6 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2514,7 +2645,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18 (6 м)</t>
+          <t>14 (6 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2539,7 +2670,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19 (6 м)</t>
+          <t>15 (6 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2564,7 +2695,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20 (6 м)</t>
+          <t>16 (6 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2589,7 +2720,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21 (6 м)</t>
+          <t>17 (6 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2614,7 +2745,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22 (6 м)</t>
+          <t>18 (6 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,21 +2770,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>23 (6 м)</t>
+          <t>19 (6 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="39">
@@ -2664,21 +2795,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24 (6 м)</t>
+          <t>20 (6 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="40">
@@ -2689,21 +2820,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>25 (6 м)</t>
+          <t>21 (6 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="41">
@@ -2714,21 +2845,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>26 (6 м)</t>
+          <t>22 (6 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="42">
@@ -2739,7 +2870,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27 (6 м)</t>
+          <t>23 (6 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2764,12 +2895,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>28 (6 м)</t>
+          <t>24 (6 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.490 + 1.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2778,31 +2909,131 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3.014</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>25 (6 м)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>26 (6 м)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>27 (6 м)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>□35×35×2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>28 (6 м)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.490 + 1.490</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3.014</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>1 (6 м)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>0.113 + 0.113</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Стойка-вставка</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E48" t="n">
         <v>5.768</v>
       </c>
     </row>
@@ -3493,7 +3724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3554,16 +3785,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.1</v>
+        <v>24.33</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.511</v>
+        <v>2.423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.857</v>
+        <v>0.855</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3583,20 +3814,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.09</v>
+        <v>26.11</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>4.073</v>
+        <v>3.715</v>
       </c>
       <c r="F3" t="n">
-        <v>0.959</v>
+        <v>0.902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>устойчивость [D+S+0.9W+x]</t>
+          <t>устойчивость [D+S+0.9W+y]</t>
         </is>
       </c>
     </row>
@@ -3612,13 +3843,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.57</v>
+        <v>0.36</v>
       </c>
       <c r="D4" t="n">
-        <v>26.35</v>
+        <v>24.98</v>
       </c>
       <c r="E4" t="n">
-        <v>0.367</v>
+        <v>0.379</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -3644,17 +3875,17 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="E5" t="n">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.31</v>
+        <v>0.284</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>узел kp→tie: продавливание грани пояса N=1.7 кН, NRd=5.4 кН</t>
+          <t>узел kp→tie: продавливание грани пояса N=1.5 кН, NRd=5.4 кН</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3901,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.61</v>
+        <v>5.53</v>
       </c>
       <c r="D6" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.896</v>
+        <v>0.893</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3699,27 +3930,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.88</v>
+        <v>1.46</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="E7" t="n">
-        <v>0.438</v>
+        <v>0.274</v>
       </c>
       <c r="F7" t="n">
-        <v>0.887</v>
+        <v>0.633</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>прочность [D+S+0.9W+x]</t>
+          <t>устойчивость [D+S+0.9W+y]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Торцевая обвязка обрешётки</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3728,76 +3959,134 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.87</v>
+        <v>1.44</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>0.166</v>
+        <v>0.601</v>
       </c>
       <c r="F8" t="n">
         <v>0.643</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>стенка c/t [D+S]</t>
+          <t>стенка c/t изг. [D+S]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Подкосы торцевой обвязки</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="n">
-        <v>17.85</v>
-      </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.092</v>
       </c>
       <c r="F9" t="n">
-        <v>0.643</v>
+        <v>0.706</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>стенка c/t изг. [D+S]</t>
+          <t>гибкость [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Стойка-вставка средней рамы</t>
+          <t>Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.97</v>
+        <v>22.55</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.95</v>
+        <v>0.254</v>
       </c>
       <c r="F10" t="n">
-        <v>0.83</v>
+        <v>0.643</v>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>стенка c/t [D+S]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>стенка c/t изг. [D+S]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Стойка-вставка средней рамы</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>□60×60×3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>устойчивость [D+S]</t>
         </is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>49265</v>
+        <v>48614</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -678,7 +678,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>4279</v>
+        <v>4206</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -700,7 +700,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>5481</v>
+        <v>5235</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>21216</v>
+        <v>20096</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -832,7 +832,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>5446</v>
+        <v>5353</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>13260</v>
+        <v>12560</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>6188</v>
+        <v>5861</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 822 кг; площадь окраски 57.6 → 44.8 м²; швы 37.6 → 31.2 м; деталей 84 → 82.</t>
+          <t>Масса металла: было 1226 кг, стало 810 кг; площадь окраски 57.6 → 44.0 м²; швы 37.6 → 29.8 м; деталей 84 → 78.</t>
         </is>
       </c>
     </row>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>153.69</v>
+        <v>132.73</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E2" t="n">
-        <v>306.1</v>
+        <v>264.3</v>
       </c>
       <c r="F2" t="n">
         <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>19519</v>
+        <v>16857</v>
       </c>
     </row>
     <row r="3">
@@ -1060,23 +1060,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Затяжки, Нижний пояс боковой фермы, Раскосы боковой фермы, Торцевая обвязка обрешётки</t>
+          <t>Затяжки, Коньковая обрешётина, Нижний пояс боковой фермы, Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.19</v>
+        <v>42.4</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>175.2</v>
+        <v>151</v>
       </c>
       <c r="F3" t="n">
         <v>226</v>
       </c>
       <c r="G3" t="n">
-        <v>11117</v>
+        <v>9582</v>
       </c>
     </row>
     <row r="4">
@@ -1136,28 +1136,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Подкосы торцевой обвязки</t>
+          <t>Карнизные обрешётины, Торцевая обвязка обрешётки</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.71</v>
+        <v>27.75</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>9.6</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="G6" t="n">
-        <v>617</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="7">
@@ -1251,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1569,14 +1569,14 @@
         <v>0.1</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>отрезок трубы внутрь стыка, по 50 мм в каждую часть</t>
+          <t>отрезок трубы внутрь стыка, по 50 мм в каждую часть (по желанию)</t>
         </is>
       </c>
     </row>
@@ -1595,10 +1595,10 @@
         <v>5.49</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>240.5</v>
+        <v>207.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         <v>1.49</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>65.3</v>
+        <v>56.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1650,7 +1650,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>26.3</v>
+        <v>17.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1676,7 +1676,7 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>22.7</v>
+        <v>14.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1687,59 +1687,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Подкос торцевой обвязки, задний свес</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.362</v>
+        <v>5.49</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6</v>
+        <v>25.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>низ — вертикальный рез к грани колонны на +2.10, верх — горизонтальный рез под обвязку (45° к горизонту)</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (на вкладыше, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Подкос торцевой обвязки, передний свес</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.348</v>
+        <v>1.49</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>низ — вертикальный рез к грани колонны на +2.10, верх — горизонтальный рез под обвязку (45° к горизонту)</t>
+          <t>торцы прямые</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1748,24 +1748,24 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.403</v>
+        <v>5.49</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>34.2</v>
+        <v>19.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (на вкладыше, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Коньковая обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1774,41 +1774,93 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.54</v>
+        <v>1.49</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>32.3</v>
+        <v>5.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+          <t>торцы прямые</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Раскос боковой фермы</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2.403</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Стойка-вставка</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C23" t="n">
         <v>0.113</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E23" t="n">
         <v>1.2</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>низ — прямой (встаёт на столик фермы), верх — под 12°</t>
         </is>
@@ -1975,16 +2027,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.397</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Затяжка средней рамы</t>
+          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="7">
@@ -2000,16 +2052,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Затяжка средней рамы</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -2050,16 +2102,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.457</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="10">
@@ -2100,16 +2152,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.698</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.299</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="12">
@@ -2125,16 +2177,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.698</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.299</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="13">
@@ -2150,16 +2202,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.186 + 2.403</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы; Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.405</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="14">
@@ -2175,41 +2227,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.186 + 2.403</t>
+          <t>1.490</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы; Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Коньковая обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.405</v>
+        <v>4.507</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.188</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="16">
@@ -2220,52 +2272,52 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
+          <t>0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Подкос фермы</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.282</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598</t>
+          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Подвеска у конька</t>
+          <t>Вкладыш стыка обрешётины</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.197</v>
+        <v>4.043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,22 +2327,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.362 + 1.362 + 1.348 + 1.348 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины; Подкос торцевой обвязки, задний свес; Подкос торцевой обвязки, передний свес</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.053</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2300,16 +2352,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.249</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="20">
@@ -2320,7 +2372,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2345,7 +2397,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2370,7 +2422,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2395,7 +2447,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2420,7 +2472,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2445,7 +2497,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>8 (6 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2470,7 +2522,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>9 (6 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2495,7 +2547,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8 (6 м)</t>
+          <t>10 (6 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2520,7 +2572,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9 (6 м)</t>
+          <t>11 (6 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2545,7 +2597,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10 (6 м)</t>
+          <t>12 (6 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2570,7 +2622,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11 (6 м)</t>
+          <t>13 (6 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2595,7 +2647,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12 (6 м)</t>
+          <t>14 (6 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2620,7 +2672,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13 (6 м)</t>
+          <t>15 (6 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2645,7 +2697,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14 (6 м)</t>
+          <t>16 (6 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2670,7 +2722,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15 (6 м)</t>
+          <t>17 (6 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2695,7 +2747,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16 (6 м)</t>
+          <t>18 (6 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2720,7 +2772,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17 (6 м)</t>
+          <t>19 (6 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2745,21 +2797,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18 (6 м)</t>
+          <t>20 (6 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="38">
@@ -2770,21 +2822,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19 (6 м)</t>
+          <t>21 (6 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="39">
@@ -2795,21 +2847,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20 (6 м)</t>
+          <t>22 (6 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="40">
@@ -2820,21 +2872,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21 (6 м)</t>
+          <t>23 (6 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="41">
@@ -2845,171 +2897,171 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22 (6 м)</t>
+          <t>24 (6 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.507</v>
+        <v>1.521</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>23 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>25 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>3.698 + 1.490</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.028</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>26 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>3.698 + 1.490</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.028</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>27 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>3.186</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.028</v>
+        <v>2.811</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>28 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.490 + 1.490</t>
+          <t>3.186</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3.014</v>
+        <v>2.811</v>
       </c>
     </row>
     <row r="48">
@@ -3445,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3697,7 +3749,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3710,6 +3762,72 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>пластиковые заглушки 35×35</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Заглушка торца карнизной обрешётины и обвязки</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>50 × 30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>торцы карнизных обрешётин (4) и обвязки у карниза (4)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>пластиковые заглушки 50×30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Заглушка торца коньковой обрешётины</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>60 × 60</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>торцы коньковой обрешётины</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>пластиковые заглушки 60×60</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3785,16 +3903,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.33</v>
+        <v>24.29</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.423</v>
+        <v>2.481</v>
       </c>
       <c r="F2" t="n">
-        <v>0.855</v>
+        <v>0.853</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3814,20 +3932,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.11</v>
+        <v>27.82</v>
       </c>
       <c r="D3" t="n">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.715</v>
+        <v>4.078</v>
       </c>
       <c r="F3" t="n">
-        <v>0.902</v>
+        <v>0.958</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>устойчивость [D+S+0.9W+y]</t>
+          <t>устойчивость [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
@@ -3843,13 +3961,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="D4" t="n">
-        <v>24.98</v>
+        <v>26.26</v>
       </c>
       <c r="E4" t="n">
-        <v>0.379</v>
+        <v>0.37</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -3875,17 +3993,17 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="E5" t="n">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.284</v>
+        <v>0.306</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>узел kp→tie: продавливание грани пояса N=1.5 кН, NRd=5.4 кН</t>
+          <t>узел kp→tie: продавливание грани пояса N=1.7 кН, NRd=5.4 кН</t>
         </is>
       </c>
     </row>
@@ -3901,16 +4019,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.53</v>
+        <v>5.42</v>
       </c>
       <c r="D6" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.893</v>
+        <v>0.889</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3930,20 +4048,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="D7" t="n">
-        <v>3.85</v>
+        <v>0.85</v>
       </c>
       <c r="E7" t="n">
-        <v>0.274</v>
+        <v>0.453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.633</v>
+        <v>0.949</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>устойчивость [D+S+0.9W+y]</t>
+          <t>устойчивость [D+S+0.9W-x]</t>
         </is>
       </c>
     </row>
@@ -3955,60 +4073,60 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.601</v>
+        <v>0.258</v>
       </c>
       <c r="F8" t="n">
-        <v>0.643</v>
+        <v>0.655</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>стенка c/t изг. [D+S]</t>
+          <t>устойчивость [D+S]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Подкосы торцевой обвязки</t>
+          <t>Карнизные обрешётины</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.28</v>
+        <v>0.6</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>0.092</v>
+        <v>0.51</v>
       </c>
       <c r="F9" t="n">
-        <v>0.706</v>
+        <v>0.734</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>гибкость [D+S+0.9W+x]</t>
+          <t>устойчивость [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Коньковая обрешётина</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4017,27 +4135,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.55</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.254</v>
+        <v>0.912</v>
       </c>
       <c r="F10" t="n">
         <v>0.643</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>стенка c/t [D+S]</t>
+          <t>стенка c/t изг. [D+S]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4046,47 +4164,76 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="n">
-        <v>18.67</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.136</v>
+        <v>0.181</v>
       </c>
       <c r="F11" t="n">
         <v>0.643</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>стенка c/t изг. [D+S]</t>
+          <t>стенка c/t [D+S]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>стенка c/t изг. [D+S]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Стойка-вставка средней рамы</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="E13" t="n">
+        <v>1.991</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>устойчивость [D+S]</t>
         </is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>48614</v>
+        <v>47095</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1055,82 +1055,82 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Затяжки, Коньковая обрешётина, Нижний пояс боковой фермы, Раскосы боковой фермы</t>
+          <t>Стропила</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.4</v>
+        <v>20.75</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>151</v>
+        <v>146.7</v>
       </c>
       <c r="F3" t="n">
-        <v>226</v>
+        <v>428</v>
       </c>
       <c r="G3" t="n">
-        <v>9582</v>
+        <v>8879</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Колонны</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.75</v>
+        <v>15.65</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>146.7</v>
+        <v>144.4</v>
       </c>
       <c r="F4" t="n">
-        <v>428</v>
+        <v>540</v>
       </c>
       <c r="G4" t="n">
-        <v>8879</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Затяжки, Коньковая обрешётина, Нижний пояс боковой фермы, Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.65</v>
+        <v>36.09</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>144.4</v>
+        <v>128.5</v>
       </c>
       <c r="F5" t="n">
-        <v>540</v>
+        <v>226</v>
       </c>
       <c r="G5" t="n">
-        <v>8453</v>
+        <v>8157</v>
       </c>
     </row>
     <row r="6">
@@ -1190,51 +1190,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Стойка-вставка средней рамы</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>315</v>
-      </c>
-      <c r="G8" t="n">
-        <v>94</v>
+          <t>ИТОГО трубы</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUM(C2:C7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUM(G2:G7)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
-        <is>
-          <t>ИТОГО трубы</t>
-        </is>
-      </c>
-      <c r="C9">
-        <f>SUM(C2:C8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>SUM(G2:G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
         <is>
           <t>Пластины (фасонки, крышки колонн): 30.1 кг × 55 грн/кг</t>
         </is>
@@ -1251,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1765,12 +1738,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 2 (стык → задний край)</t>
+          <t>Коньковая обрешётина, часть 2 (стык → задний край) — из обрезка заказчика</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1780,11 +1753,11 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>торцы прямые</t>
+          <t>торцы прямые; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
         </is>
       </c>
     </row>
@@ -1803,10 +1776,10 @@
         <v>2.403</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>34.2</v>
+        <v>17.1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1817,50 +1790,76 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Раскос боковой фермы — из обрезка заказчика</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.54</v>
+        <v>2.403</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>32.3</v>
+        <v>24.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Стойка-вставка</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.113</v>
+        <v>4.54</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Стойка-вставка — из обрезка заказчика</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>□60×60×3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
         <v>1.2</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>низ — прямой (встаёт на столик фермы), верх — под 12°</t>
         </is>
@@ -1877,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1917,201 +1916,193 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□60×60×3 (обрезки заказчика)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>обрезок 1.74 м</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.013 + 3.993 + 3.833</t>
+          <t>1.490 + 0.113 + 0.113</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Колонна Л3; Колонна П1; Колонна П3</t>
+          <t>Коньковая обрешётина, часть 2 (стык → задний край) — из обрезка заказчика; Стойка-вставка — из обрезка заказчика</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.152</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□60×60×3 (обрезки заказчика)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.803</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Колонна Л1</t>
-        </is>
-      </c>
+          <t>обрезок 2.05 м</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>8.194000000000001</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×3 (обрезки заказчика)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>обрезок 2.70 м</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.710 + 3.710 + 3.710</t>
+          <t>2.403</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Раскос боковой фермы — из обрезка заказчика</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.861</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×3 (обрезки заказчика)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
+          <t>обрезок 2.80 м</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.199 + 3.199 + 3.199</t>
+          <t>2.403</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Раскос боковой фермы — из обрезка заказчика</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.394</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>1 (12 м)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>4.013 + 3.993 + 3.833</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
+          <t>Колонна Л3; Колонна П1; Колонна П3</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.507</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>2 (12 м)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.397</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Затяжка средней рамы</t>
+          <t>Колонна Л1</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6</v>
+        <v>8.194000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>1 (12 м)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>3.710 + 3.710 + 3.710</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.64</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>2 (12 м)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>3.199 + 3.199 + 3.199</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.64</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="10">
@@ -2122,21 +2113,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.457</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="11">
@@ -2147,21 +2138,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Затяжка средней рамы</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.457</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -2172,21 +2163,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.188</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="13">
@@ -2197,21 +2188,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.188</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="14">
@@ -2222,77 +2213,77 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.490</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 2 (стык → задний край)</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.507</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Подкос фермы</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.282</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Подвеска у конька</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.197</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2302,66 +2293,66 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.043</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.507</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Вкладыш стыка обрешётины</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.507</v>
+        <v>4.043</v>
       </c>
     </row>
     <row r="20">
@@ -2372,7 +2363,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2397,7 +2388,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2422,7 +2413,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2447,7 +2438,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2472,7 +2463,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2497,7 +2488,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2522,7 +2513,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2547,7 +2538,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10 (6 м)</t>
+          <t>8 (6 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2572,7 +2563,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11 (6 м)</t>
+          <t>9 (6 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2597,7 +2588,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12 (6 м)</t>
+          <t>10 (6 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2622,7 +2613,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13 (6 м)</t>
+          <t>11 (6 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2647,7 +2638,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14 (6 м)</t>
+          <t>12 (6 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2672,7 +2663,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15 (6 м)</t>
+          <t>13 (6 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2697,7 +2688,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16 (6 м)</t>
+          <t>14 (6 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2722,7 +2713,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17 (6 м)</t>
+          <t>15 (6 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2747,7 +2738,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18 (6 м)</t>
+          <t>16 (6 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2772,7 +2763,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19 (6 м)</t>
+          <t>17 (6 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2797,21 +2788,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20 (6 м)</t>
+          <t>18 (6 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="38">
@@ -2822,21 +2813,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21 (6 м)</t>
+          <t>19 (6 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="39">
@@ -2847,7 +2838,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22 (6 м)</t>
+          <t>20 (6 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2872,7 +2863,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>23 (6 м)</t>
+          <t>21 (6 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2897,12 +2888,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24 (6 м)</t>
+          <t>22 (6 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2911,57 +2902,57 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.521</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>□50×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>23 (6 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>□50×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>24 (6 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.507</v>
+        <v>1.521</v>
       </c>
     </row>
     <row r="44">
@@ -2972,21 +2963,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.698 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.806</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="45">
@@ -2997,21 +2988,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.698 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.806</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="46">
@@ -3022,21 +3013,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.186</t>
+          <t>3.698 + 1.490</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.811</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="47">
@@ -3047,46 +3038,71 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.186</t>
+          <t>3.698 + 1.490</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.811</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.113 + 0.113</t>
+          <t>3.186</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Стойка-вставка</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5.768</v>
+        <v>2.811</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>□50×30×2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6 (6 м)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3.186</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2.811</v>
       </c>
     </row>
   </sheetData>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>47095</v>
+        <v>47178</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -678,7 +678,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>4206</v>
+        <v>4213</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -700,7 +700,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>5235</v>
+        <v>5277</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>20096</v>
+        <v>20153</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -832,7 +832,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>5353</v>
+        <v>5362</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>12560</v>
+        <v>12596</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>5861</v>
+        <v>5878</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 810 кг; площадь окраски 57.6 → 44.0 м²; швы 37.6 → 29.8 м; деталей 84 → 78.</t>
+          <t>Масса металла: было 1226 кг, стало 812 кг; площадь окраски 57.6 → 44.1 м²; швы 37.6 → 30.0 м; деталей 84 → 78.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1168,46 +1168,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька), Подкосы фермы</t>
+          <t>Подкосы фермы</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.69</v>
+        <v>6.65</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
         <v>67.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>586</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ИТОГО трубы</t>
-        </is>
-      </c>
-      <c r="C8">
-        <f>SUM(C2:C7)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>SUM(G2:G7)</f>
-        <v/>
+          <t>□30×30×2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Подвеска (стойка у конька)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>108</v>
+      </c>
+      <c r="G8" t="n">
+        <v>221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>ИТОГО трубы</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUM(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUM(G2:G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Пластины (фасонки, крышки колонн): 30.1 кг × 55 грн/кг</t>
         </is>
@@ -1483,7 +1510,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1493,7 +1520,7 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1876,7 +1903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1946,13 +1973,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>обрезок 2.05 м</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>обрезок 2.70 м</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.403</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Раскос боковой фермы — из обрезка заказчика</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>2.05</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="4">
@@ -1963,7 +1998,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>обрезок 2.70 м</t>
+          <t>обрезок 2.80 м</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1977,32 +2012,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.294</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>□60×60×3 (обрезки заказчика)</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>обрезок 2.80 м</t>
+          <t>1 (12 м)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.403</t>
+          <t>4.013 + 3.993 + 3.833</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы — из обрезка заказчика</t>
+          <t>Колонна Л3; Колонна П1; Колонна П3</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.394</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="6">
@@ -2013,46 +2048,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>2 (12 м)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.013 + 3.993 + 3.833</t>
+          <t>3.803</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Колонна Л3; Колонна П1; Колонна П3</t>
+          <t>Колонна Л1</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.152</v>
+        <v>8.194000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
+          <t>1 (12 м)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.803</t>
+          <t>3.710 + 3.710 + 3.710</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Колонна Л1</t>
+          <t>Стропило длинное (свес 0.90)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.194000000000001</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="8">
@@ -2063,46 +2098,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1 (12 м)</t>
+          <t>2 (12 м)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.710 + 3.710 + 3.710</t>
+          <t>3.199 + 3.199 + 3.199</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Стропило длинное (свес 0.90)</t>
+          <t>Стропило короткое (свес 0.40)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.861</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2 (12 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.199 + 3.199 + 3.199</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Стропило короткое (свес 0.40)</t>
+          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.394</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="10">
@@ -2113,21 +2148,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
+          <t>Затяжка средней рамы</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.507</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -2138,21 +2173,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.397</t>
+          <t>5.357</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Затяжка средней рамы</t>
+          <t>Затяжка крайней рамы</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="12">
@@ -2163,7 +2198,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2188,21 +2223,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.357</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Затяжка крайней рамы</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.64</v>
+        <v>1.457</v>
       </c>
     </row>
     <row r="14">
@@ -2213,7 +2248,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2238,46 +2273,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>2.403 + 2.403</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.457</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.403 + 2.403</t>
+          <t>0.598 + 0.598 + 0.598 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Вкладыш стыка обрешётины; Подвеска у конька</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.188</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="17">
@@ -2308,51 +2343,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Подвеска у конька</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.197</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.043</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="20">
@@ -2363,7 +2398,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2388,7 +2423,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2413,7 +2448,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2438,7 +2473,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2463,7 +2498,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2488,7 +2523,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>8 (6 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2513,7 +2548,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>9 (6 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2538,7 +2573,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8 (6 м)</t>
+          <t>10 (6 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2563,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9 (6 м)</t>
+          <t>11 (6 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2588,7 +2623,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10 (6 м)</t>
+          <t>12 (6 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2613,7 +2648,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11 (6 м)</t>
+          <t>13 (6 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2638,7 +2673,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12 (6 м)</t>
+          <t>14 (6 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2663,7 +2698,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13 (6 м)</t>
+          <t>15 (6 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2688,7 +2723,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14 (6 м)</t>
+          <t>16 (6 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2713,7 +2748,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15 (6 м)</t>
+          <t>17 (6 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2738,7 +2773,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16 (6 м)</t>
+          <t>18 (6 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2763,7 +2798,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17 (6 м)</t>
+          <t>19 (6 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2788,21 +2823,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18 (6 м)</t>
+          <t>20 (6 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="38">
@@ -2813,21 +2848,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19 (6 м)</t>
+          <t>21 (6 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.507</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="39">
@@ -2838,7 +2873,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20 (6 м)</t>
+          <t>22 (6 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2863,7 +2898,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21 (6 м)</t>
+          <t>23 (6 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2888,12 +2923,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22 (6 м)</t>
+          <t>24 (6 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2902,57 +2937,57 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.028</v>
+        <v>1.521</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>23 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>24 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.521</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="44">
@@ -2963,21 +2998,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>3.698 + 1.490</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.507</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="45">
@@ -2988,21 +3023,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>3.698 + 1.490</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.507</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="46">
@@ -3013,21 +3048,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.698 + 1.490</t>
+          <t>3.186</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.806</v>
+        <v>2.811</v>
       </c>
     </row>
     <row r="47">
@@ -3038,70 +3073,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.698 + 1.490</t>
+          <t>3.186</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.806</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>□50×30×2</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>5 (6 м)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3.186</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>2.811</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>□50×30×2</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>6 (6 м)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3.186</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
         <v>2.811</v>
       </c>
     </row>
@@ -3919,13 +3904,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.29</v>
+        <v>24.3</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.481</v>
+        <v>2.484</v>
       </c>
       <c r="F2" t="n">
         <v>0.853</v>
@@ -3948,13 +3933,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.82</v>
+        <v>27.83</v>
       </c>
       <c r="D3" t="n">
         <v>1.09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.078</v>
+        <v>4.076</v>
       </c>
       <c r="F3" t="n">
         <v>0.958</v>
@@ -3980,10 +3965,10 @@
         <v>0.31</v>
       </c>
       <c r="D4" t="n">
-        <v>26.26</v>
+        <v>26.27</v>
       </c>
       <c r="E4" t="n">
-        <v>0.37</v>
+        <v>0.374</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -4002,24 +3987,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>□20×20×2</t>
+          <t>□30×30×2</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="E5" t="n">
-        <v>0.018</v>
+        <v>0.044</v>
       </c>
       <c r="F5" t="n">
-        <v>0.306</v>
+        <v>0.286</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>узел kp→tie: продавливание грани пояса N=1.7 кН, NRd=5.4 кН</t>
+          <t>стенка c/t изг. [D+S]</t>
         </is>
       </c>
     </row>
@@ -4035,13 +4020,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.42</v>
+        <v>5.43</v>
       </c>
       <c r="D6" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F6" t="n">
         <v>0.889</v>
@@ -4064,16 +4049,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="D7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="E7" t="n">
         <v>0.453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4096,13 +4081,13 @@
         <v>1.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E8" t="n">
         <v>0.258</v>
       </c>
       <c r="F8" t="n">
-        <v>0.655</v>
+        <v>0.656</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4154,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="E10" t="n">
-        <v>0.912</v>
+        <v>0.916</v>
       </c>
       <c r="F10" t="n">
         <v>0.643</v>
@@ -4180,7 +4165,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.02</v>
+        <v>21.03</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -4244,10 +4229,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.991</v>
+        <v>1.995</v>
       </c>
       <c r="F13" t="n">
-        <v>0.847</v>
+        <v>0.849</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>47178</v>
+        <v>47095</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -678,7 +678,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>4213</v>
+        <v>4206</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -700,7 +700,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>5277</v>
+        <v>5235</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>20153</v>
+        <v>20096</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -832,7 +832,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>5362</v>
+        <v>5353</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>12596</v>
+        <v>12560</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>5878</v>
+        <v>5861</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 812 кг; площадь окраски 57.6 → 44.1 м²; швы 37.6 → 30.0 м; деталей 84 → 78.</t>
+          <t>Масса металла: было 1226 кг, стало 810 кг; площадь окраски 57.6 → 44.0 м²; швы 37.6 → 29.8 м; деталей 84 → 78.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1168,73 +1168,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Подкосы фермы</t>
+          <t>Подвеска (стойка у конька), Подкосы фермы</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.65</v>
+        <v>8.69</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="F7" t="n">
         <v>67.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>448</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Подвеска (стойка у конька)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>108</v>
-      </c>
-      <c r="G8" t="n">
-        <v>221</v>
+          <t>ИТОГО трубы</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUM(C2:C7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E2:E7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUM(G2:G7)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
-        <is>
-          <t>ИТОГО трубы</t>
-        </is>
-      </c>
-      <c r="C9">
-        <f>SUM(C2:C8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>SUM(G2:G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
         <is>
           <t>Пластины (фасонки, крышки колонн): 30.1 кг × 55 грн/кг</t>
         </is>
@@ -1251,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1510,7 +1483,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1520,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,33 +1530,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1</v>
+        <v>5.49</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2</v>
+        <v>207.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>отрезок трубы внутрь стыка, по 50 мм в каждую часть (по желанию)</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1592,43 +1565,43 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.49</v>
+        <v>1.49</v>
       </c>
       <c r="D13" t="n">
         <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>207.7</v>
+        <v>56.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (на вкладыше, см. узлы)</t>
+          <t>торцы прямые</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.49</v>
+        <v>3.698</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>56.4</v>
+        <v>17.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>торцы прямые</t>
+          <t>у карниза — прямой рез, у конька — вертикальный рез (78° к оси) встык со второй половиной</t>
         </is>
       </c>
     </row>
@@ -1644,13 +1617,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.698</v>
+        <v>3.186</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>17.1</v>
+        <v>14.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1661,7 +1634,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1670,24 +1643,24 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.186</v>
+        <v>5.49</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7</v>
+        <v>25.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>у карниза — прямой рез, у конька — вертикальный рез (78° к оси) встык со второй половиной</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1696,107 +1669,107 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.49</v>
+        <v>1.49</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>25.3</v>
+        <v>6.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (на вкладыше, см. узлы)</t>
+          <t>торцы прямые</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край)</t>
+          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>□50×30×2</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.49</v>
+        <v>5.49</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>6.9</v>
+        <v>19.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>торцы прямые</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
+          <t>Коньковая обрешётина, часть 2 (стык → задний край) — из обрезка заказчика</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.49</v>
+        <v>1.49</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>19.6</v>
+        <v>7.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (на вкладыше, см. узлы)</t>
+          <t>торцы прямые; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 2 (стык → задний край) — из обрезка заказчика</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.49</v>
+        <v>2.403</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>7.7</v>
+        <v>17.1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>торцы прямые; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Раскос боковой фермы — из обрезка заказчика</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1806,87 +1779,61 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>17.1</v>
+        <v>24.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы — из обрезка заказчика</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.403</v>
+        <v>4.54</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>24.9</v>
+        <v>32.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
+          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Стойка-вставка — из обрезка заказчика</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.54</v>
+        <v>0.113</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>32.3</v>
+        <v>1.2</v>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Стойка-вставка — из обрезка заказчика</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>□60×60×3</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F24" t="inlineStr">
         <is>
           <t>низ — прямой (встаёт на столик фермы), верх — под 12°</t>
         </is>
@@ -2293,7 +2240,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2303,16 +2250,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100 + 0.100</t>
+          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Вкладыш стыка обрешётины; Подвеска у конька</t>
+          <t>Подкос фермы</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.24</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="17">
@@ -2323,21 +2270,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.950 + 0.950 + 0.950 + 0.950 + 0.950 + 0.950</t>
+          <t>0.598 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Подкос фермы</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.282</v>
+        <v>4.197</v>
       </c>
     </row>
     <row r="18">
@@ -3904,13 +3851,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.3</v>
+        <v>24.29</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.484</v>
+        <v>2.481</v>
       </c>
       <c r="F2" t="n">
         <v>0.853</v>
@@ -3933,13 +3880,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.83</v>
+        <v>27.82</v>
       </c>
       <c r="D3" t="n">
         <v>1.09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.076</v>
+        <v>4.078</v>
       </c>
       <c r="F3" t="n">
         <v>0.958</v>
@@ -3965,10 +3912,10 @@
         <v>0.31</v>
       </c>
       <c r="D4" t="n">
-        <v>26.27</v>
+        <v>26.26</v>
       </c>
       <c r="E4" t="n">
-        <v>0.374</v>
+        <v>0.37</v>
       </c>
       <c r="F4" t="n">
         <v>0.772</v>
@@ -3987,24 +3934,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>□30×30×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="E5" t="n">
-        <v>0.044</v>
+        <v>0.018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.286</v>
+        <v>0.306</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>стенка c/t изг. [D+S]</t>
+          <t>узел kp→tie: продавливание грани пояса N=1.7 кН, NRd=5.4 кН</t>
         </is>
       </c>
     </row>
@@ -4020,13 +3967,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="D6" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>0.889</v>
@@ -4049,16 +3996,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="D7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="E7" t="n">
         <v>0.453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4081,13 +4028,13 @@
         <v>1.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
         <v>0.258</v>
       </c>
       <c r="F8" t="n">
-        <v>0.656</v>
+        <v>0.655</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4139,10 +4086,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.916</v>
+        <v>0.912</v>
       </c>
       <c r="F10" t="n">
         <v>0.643</v>
@@ -4165,7 +4112,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.03</v>
+        <v>21.02</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -4229,10 +4176,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.995</v>
+        <v>1.991</v>
       </c>
       <c r="F13" t="n">
-        <v>0.849</v>
+        <v>0.847</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -3445,7 +3445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3749,31 +3749,64 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Пруток Ø6 под коньковую обрешётину</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ø6: 6 × 60 + 4 × 30 мм</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>клиновой зазор под коньковой обрешётиной на стропилах (6) и на обвязке (4)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>катанка / арматура Ø6, ≈ 0.5 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Заглушка торца коньковой обрешётины</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>60 × 60</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>торцы коньковой обрешётины</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>пластиковые заглушки 60×60</t>
         </is>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>47095</v>
+        <v>48094</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -524,7 +524,7 @@
         <v>3000</v>
       </c>
       <c r="C4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f>C4-B4</f>
@@ -678,7 +678,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>4206</v>
+        <v>4233</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>20096</v>
+        <v>20116</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -832,7 +832,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>5353</v>
+        <v>5387</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>12560</v>
+        <v>12572</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>5861</v>
+        <v>5867</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 810 кг; площадь окраски 57.6 → 44.0 м²; швы 37.6 → 29.8 м; деталей 84 → 78.</t>
+          <t>Масса металла: было 1226 кг, стало 828 кг; площадь окраски 57.6 → 44.3 м²; швы 37.6 → 29.8 м; деталей 84 → 78.</t>
         </is>
       </c>
     </row>
@@ -1055,55 +1055,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>□100×60×3</t>
+          <t>□100×60×4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Стропила</t>
+          <t>Колонны</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.75</v>
+        <v>17.5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>146.7</v>
+        <v>161.4</v>
       </c>
       <c r="F3" t="n">
-        <v>428</v>
+        <v>540</v>
       </c>
       <c r="G3" t="n">
-        <v>8879</v>
+        <v>9452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>□100×60×4</t>
+          <t>□100×60×3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Колонны</t>
+          <t>Стропила</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.65</v>
+        <v>20.75</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>144.4</v>
+        <v>146.7</v>
       </c>
       <c r="F4" t="n">
-        <v>540</v>
+        <v>428</v>
       </c>
       <c r="G4" t="n">
-        <v>8453</v>
+        <v>8879</v>
       </c>
     </row>
     <row r="5">
@@ -1279,17 +1279,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.803</v>
+        <v>4.203</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>35.1</v>
+        <v>38.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 1.10 м (на всю глубину лунки, низ на 10 см выше дна)</t>
         </is>
       </c>
     </row>
@@ -1305,17 +1305,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.993</v>
+        <v>4.393</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>36.8</v>
+        <v>40.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 1.10 м (на всю глубину лунки, низ на 10 см выше дна)</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.833</v>
+        <v>4.333</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>35.3</v>
+        <v>40</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 1.20 м (на всю глубину лунки, низ на 10 см выше дна)</t>
         </is>
       </c>
     </row>
@@ -1357,17 +1357,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.013</v>
+        <v>4.563</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>42.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 0.70 м</t>
+          <t>низ — прямой рез (+ заглушка), верх — под 12° по низу стропила; в бетоне 1.25 м (на всю глубину лунки, низ на 10 см выше дна)</t>
         </is>
       </c>
     </row>
@@ -1975,16 +1975,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.013 + 3.993 + 3.833</t>
+          <t>4.563 + 4.393</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Колонна Л3; Колонна П1; Колонна П3</t>
+          <t>Колонна Л3; Колонна П3</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.152</v>
+        <v>3.038</v>
       </c>
     </row>
     <row r="6">
@@ -2000,16 +2000,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.803</t>
+          <t>4.333 + 4.203</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Колонна Л1</t>
+          <t>Колонна Л1; Колонна П1</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8.194000000000001</v>
+        <v>3.458</v>
       </c>
     </row>
     <row r="7">

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -3101,17 +3101,17 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="D2" t="n">
         <v>1100</v>
       </c>
       <c r="E2" t="n">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>передняя кромка 0→157 мм</t>
+          <t>передняя кромка 0→156 мм</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="D3" t="n">
         <v>1100</v>
@@ -3149,7 +3149,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="D4" t="n">
         <v>1100</v>
@@ -3173,7 +3173,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="D5" t="n">
         <v>1100</v>
@@ -3197,7 +3197,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="D6" t="n">
         <v>1100</v>
@@ -3221,7 +3221,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="D7" t="n">
         <v>1100</v>
@@ -3245,17 +3245,17 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="D8" t="n">
         <v>380</v>
       </c>
       <c r="E8" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>задняя кромка 720→562 мм</t>
+          <t>задняя кромка 720→563 мм</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.721</v>
+        <v>3.701</v>
       </c>
       <c r="D9" t="n">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E9" t="n">
         <v>1100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>передняя кромка 182→0 мм</t>
+          <t>передняя кромка 181→0 мм</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.721</v>
+        <v>3.701</v>
       </c>
       <c r="D10" t="n">
         <v>1100</v>
@@ -3317,7 +3317,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>3.721</v>
+        <v>3.701</v>
       </c>
       <c r="D11" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>3.721</v>
+        <v>3.701</v>
       </c>
       <c r="D12" t="n">
         <v>1100</v>
@@ -3365,7 +3365,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>3.721</v>
+        <v>3.701</v>
       </c>
       <c r="D13" t="n">
         <v>1100</v>
@@ -3389,7 +3389,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>3.721</v>
+        <v>3.701</v>
       </c>
       <c r="D14" t="n">
         <v>1100</v>
@@ -3413,24 +3413,24 @@
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>3.721</v>
+        <v>3.701</v>
       </c>
       <c r="D15" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E15" t="n">
         <v>380</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>задняя кромка 537→720 мм</t>
+          <t>задняя кромка 538→720 мм</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Итого 14 листов; площадь по габаритной ширине 1.18 м — 57.2 м², по полезной — 53.4 м²; кровля 48.2 м². Укладка от переднего края (дорога).</t>
+          <t>Итого 14 листов; площадь по габаритной ширине 1.18 м — 56.9 м², по полезной — 53.1 м²; кровля 48.2 м². Укладка от переднего края (дорога).</t>
         </is>
       </c>
     </row>

--- a/output/smeta_optimized.xlsx
+++ b/output/smeta_optimized.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ведомость металла" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Детали" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Раскрой на хлысты" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Металлочерепица" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Пластины" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Проверки" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Варианты схем" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Нагрузки" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ведомость металла" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Детали" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Раскрой на хлысты" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Металлочерепица" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пластины" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Проверки" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Варианты схем" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузки" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +480,7 @@
         <v>75812</v>
       </c>
       <c r="C2" t="n">
-        <v>48094</v>
+        <v>48497</v>
       </c>
       <c r="D2">
         <f>C2-B2</f>
@@ -678,7 +678,7 @@
         <v>5500</v>
       </c>
       <c r="C11" t="n">
-        <v>4233</v>
+        <v>4274</v>
       </c>
       <c r="D11">
         <f>C11-B11</f>
@@ -700,7 +700,7 @@
         <v>6600</v>
       </c>
       <c r="C12" t="n">
-        <v>5235</v>
+        <v>5389</v>
       </c>
       <c r="D12">
         <f>C12-B12</f>
@@ -810,7 +810,7 @@
         <v>24000</v>
       </c>
       <c r="C17" t="n">
-        <v>20116</v>
+        <v>21500</v>
       </c>
       <c r="D17">
         <f>C17-B17</f>
@@ -832,7 +832,7 @@
         <v>7000</v>
       </c>
       <c r="C18" t="n">
-        <v>5387</v>
+        <v>5440</v>
       </c>
       <c r="D18">
         <f>C18-B18</f>
@@ -854,7 +854,7 @@
         <v>15000</v>
       </c>
       <c r="C19" t="n">
-        <v>12572</v>
+        <v>13437</v>
       </c>
       <c r="D19">
         <f>C19-B19</f>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
       <c r="C22" t="n">
-        <v>5867</v>
+        <v>6271</v>
       </c>
       <c r="D22">
         <f>C22-B22</f>
@@ -961,7 +961,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Масса металла: было 1226 кг, стало 828 кг; площадь окраски 57.6 → 44.3 м²; швы 37.6 → 29.8 м; деталей 84 → 78.</t>
+          <t>Масса металла: было 1226 кг, стало 834 кг; площадь окраски 57.6 → 44.7 м²; швы 37.6 → 30.7 м; деталей 84 → 84.</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Подвеска (стойка у конька), Подкосы фермы</t>
+          <t>Доп. решётка ферм у опор, Подвеска (стойка у конька), Подкосы фермы</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.69</v>
+        <v>14.67</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>9.1</v>
+        <v>15.4</v>
       </c>
       <c r="F7" t="n">
         <v>67.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>586</v>
+        <v>989</v>
       </c>
     </row>
     <row r="8">
@@ -1224,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1530,33 +1530,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Раскос фермы у опоры</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.49</v>
+        <v>0.747</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>207.7</v>
+        <v>4.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
+          <t>низ — под 28° к оси (на затяжку в 0.85 м от оси колонны), верх — под 16° (на стропило в узле подкоса)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,43 +1565,43 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.49</v>
+        <v>5.49</v>
       </c>
       <c r="D13" t="n">
         <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>56.4</v>
+        <v>207.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>торцы прямые</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>□50×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.698</v>
+        <v>1.49</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>17.1</v>
+        <v>56.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>у карниза — прямой рез, у конька — вертикальный рез (78° к оси) встык со второй половиной</t>
+          <t>торцы прямые</t>
         </is>
       </c>
     </row>
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.186</v>
+        <v>3.698</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>14.7</v>
+        <v>17.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1643,24 +1643,24 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.49</v>
+        <v>3.186</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>25.3</v>
+        <v>14.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
+          <t>у карниза — прямой рез, у конька — вертикальный рез (78° к оси) встык со второй половиной</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1669,107 +1669,107 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.49</v>
+        <v>5.49</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>6.9</v>
+        <v>25.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>торцы прямые</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.49</v>
+        <v>1.49</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>19.6</v>
+        <v>6.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
+          <t>торцы прямые</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина, часть 2 (стык → задний край) — из обрезка заказчика</t>
+          <t>Коньковая обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.49</v>
+        <v>5.49</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>7.7</v>
+        <v>19.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>торцы прямые; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
+          <t>торцы прямые; стык с частью 2 — в пролёте, в 290 мм от стропила рамы 3 (встык, см. узлы)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы</t>
+          <t>Коньковая обрешётина, часть 2 (стык → задний край) — из обрезка заказчика</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.403</v>
+        <v>1.49</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>17.1</v>
+        <v>7.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
+          <t>торцы прямые; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Раскос боковой фермы — из обрезка заказчика</t>
+          <t>Раскос боковой фермы</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1779,61 +1779,87 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>24.9</v>
+        <v>17.1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Раскос боковой фермы — из обрезка заказчика</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□60×60×3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.54</v>
+        <v>2.403</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>32.3</v>
+        <v>24.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+          <t>оба торца — горизонтальные резы под 20.7° к оси (рез по грани 170 мм): низ — на пояс, верх — под столик; □60×60×3 вместо □60×60×2 — размеры и резы те же</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Стойка-вставка — из обрезка заказчика</t>
+          <t>Нижний пояс боковой фермы</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>□60×60×3</t>
+          <t>□60×60×2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.113</v>
+        <v>4.54</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>оба торца — прямые; по фактическому расстоянию между гранями колонн</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Стойка-вставка — из обрезка заказчика</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>□60×60×3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
         <v>1.2</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>низ — прямой (встаёт на столик фермы), верх — под 12°</t>
         </is>
@@ -1850,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2275,41 +2301,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.598 + 0.598 + 0.598</t>
+          <t>0.747 + 0.747 + 0.747 + 0.747 + 0.747 + 0.747 + 0.598 + 0.598</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Подвеска у конька</t>
+          <t>Подвеска у конька; Раскос фермы у опоры</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.197</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>0.598</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 1 (передний край → стык)</t>
+          <t>Подвеска у конька</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.507</v>
+        <v>5.399</v>
       </c>
     </row>
     <row r="19">
@@ -2320,7 +2346,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2345,7 +2371,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2370,7 +2396,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2395,7 +2421,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2420,7 +2446,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6 (6 м)</t>
+          <t>5 (6 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2445,7 +2471,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7 (6 м)</t>
+          <t>6 (6 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2470,7 +2496,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8 (6 м)</t>
+          <t>7 (6 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2495,7 +2521,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9 (6 м)</t>
+          <t>8 (6 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2520,7 +2546,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10 (6 м)</t>
+          <t>9 (6 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2545,7 +2571,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11 (6 м)</t>
+          <t>10 (6 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2570,7 +2596,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12 (6 м)</t>
+          <t>11 (6 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2595,7 +2621,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13 (6 м)</t>
+          <t>12 (6 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2620,7 +2646,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14 (6 м)</t>
+          <t>13 (6 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2645,7 +2671,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15 (6 м)</t>
+          <t>14 (6 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2670,7 +2696,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16 (6 м)</t>
+          <t>15 (6 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2695,7 +2721,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17 (6 м)</t>
+          <t>16 (6 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2720,7 +2746,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18 (6 м)</t>
+          <t>17 (6 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2745,7 +2771,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19 (6 м)</t>
+          <t>18 (6 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2770,21 +2796,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20 (6 м)</t>
+          <t>19 (6 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Обрешётина, часть 2 (стык → задний край)</t>
+          <t>Обрешётина, часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.028</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="38">
@@ -2795,7 +2821,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21 (6 м)</t>
+          <t>20 (6 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2820,7 +2846,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22 (6 м)</t>
+          <t>21 (6 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2845,7 +2871,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>23 (6 м)</t>
+          <t>22 (6 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,12 +2896,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24 (6 м)</t>
+          <t>23 (6 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.490 + 1.490 + 1.490</t>
+          <t>1.490 + 1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2884,32 +2910,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.521</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>□50×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1 (6 м)</t>
+          <t>24 (6 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>1.490 + 1.490 + 1.490</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
+          <t>Обрешётина, часть 2 (стык → задний край)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.507</v>
+        <v>1.521</v>
       </c>
     </row>
     <row r="43">
@@ -2920,7 +2946,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2 (6 м)</t>
+          <t>1 (6 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2945,21 +2971,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3 (6 м)</t>
+          <t>2 (6 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.698 + 1.490</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Карнизная обрешётина (на ребро), часть 1 (передний край → стык)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.806</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="45">
@@ -2970,7 +2996,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4 (6 м)</t>
+          <t>3 (6 м)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2995,21 +3021,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5 (6 м)</t>
+          <t>4 (6 м)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.186</t>
+          <t>3.698 + 1.490</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+          <t>Карнизная обрешётина (на ребро), часть 2 (стык → задний край); Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.811</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="47">
@@ -3020,20 +3046,45 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>5 (6 м)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.186</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Торцевая обвязка (по скату, под обрешёткой)</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2.811</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>□50×30×2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>6 (6 м)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>3.186</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Торцевая обвязка (по скату, под обрешёткой)</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E48" t="n">
         <v>2.811</v>
       </c>
     </row>
@@ -3823,7 +3874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3884,20 +3935,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.29</v>
+        <v>24.32</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2.481</v>
+        <v>2.341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.853</v>
+        <v>0.834</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>гибкость [D+S]</t>
+          <t>гибкость [D+S+0.9W+y]</t>
         </is>
       </c>
     </row>
@@ -3913,16 +3964,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.82</v>
+        <v>25.47</v>
       </c>
       <c r="D3" t="n">
-        <v>1.09</v>
+        <v>1.88</v>
       </c>
       <c r="E3" t="n">
-        <v>4.078</v>
+        <v>3.591</v>
       </c>
       <c r="F3" t="n">
-        <v>0.958</v>
+        <v>0.842</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3942,20 +3993,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.31</v>
+        <v>2.36</v>
       </c>
       <c r="D4" t="n">
-        <v>26.26</v>
+        <v>26.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.37</v>
+        <v>1.186</v>
       </c>
       <c r="F4" t="n">
-        <v>0.772</v>
+        <v>0.789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>гибкость [0.95D+W-x]</t>
+          <t>прочность [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
@@ -3971,20 +4022,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>0.018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.306</v>
+        <v>0.526</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>узел kp→tie: продавливание грани пояса N=1.7 кН, NRd=5.4 кН</t>
+          <t>гибкость [0.95D+W-x]</t>
         </is>
       </c>
     </row>
@@ -4000,16 +4051,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="D6" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.889</v>
+        <v>0.893</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4020,65 +4071,65 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Обрешётка</t>
+          <t>Доп. решётка ферм у опор</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>□35×35×2</t>
+          <t>□20×20×2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.75</v>
+        <v>4.47</v>
       </c>
       <c r="D7" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="E7" t="n">
-        <v>0.453</v>
+        <v>0.02</v>
       </c>
       <c r="F7" t="n">
-        <v>0.949</v>
+        <v>0.769</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>устойчивость [D+S+0.9W-x]</t>
+          <t>гибкость [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Торцевая обвязка обрешётки</t>
+          <t>Обрешётка</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>□50×30×2</t>
+          <t>□35×35×2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>0.87</v>
       </c>
       <c r="E8" t="n">
-        <v>0.258</v>
+        <v>0.446</v>
       </c>
       <c r="F8" t="n">
-        <v>0.655</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>устойчивость [D+S]</t>
+          <t>устойчивость [D+S+0.9W-x]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Карнизные обрешётины</t>
+          <t>Торцевая обвязка обрешётки</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4087,56 +4138,56 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>1.29</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.51</v>
+        <v>0.262</v>
       </c>
       <c r="F9" t="n">
-        <v>0.734</v>
+        <v>0.659</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>устойчивость [D+S+0.9W+x]</t>
+          <t>устойчивость [D+S]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Коньковая обрешётина</t>
+          <t>Карнизные обрешётины</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>□60×60×2</t>
+          <t>□50×30×2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="n">
-        <v>3.08</v>
+        <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.912</v>
+        <v>0.517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.643</v>
+        <v>0.742</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>стенка c/t изг. [D+S]</t>
+          <t>устойчивость [D+S+0.9W+x]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Раскосы боковой фермы</t>
+          <t>Коньковая обрешётина</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4145,27 +4196,27 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.02</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="E11" t="n">
-        <v>0.181</v>
+        <v>0.914</v>
       </c>
       <c r="F11" t="n">
         <v>0.643</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>стенка c/t [D+S]</t>
+          <t>стенка c/t изг. [D+S]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Нижний пояс боковой фермы</t>
+          <t>Раскосы боковой фермы</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4174,47 +4225,76 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="n">
-        <v>18.01</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.128</v>
+        <v>0.183</v>
       </c>
       <c r="F12" t="n">
         <v>0.643</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>стенка c/t изг. [D+S]</t>
+          <t>стенка c/t [D+S]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Нижний пояс боковой фермы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>□60×60×2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>стенка c/t изг. [D+S]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Стойка-вставка средней рамы</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>□60×60×3</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>14</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>1.991</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="E14" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>устойчивость [D+S]</t>
         </is>
